--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$N$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$N$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -67,12 +67,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -708,34 +708,34 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>CONCORDIA — MUNICIPALIDAD DE PUERTO YERUA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CONCURSO DE PRECIOS</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>286/2026</t>
+          <t>1/2026</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANO DE OBRA PARA CAMBIO DE CHAPAS EN TECHO</t>
+          <t>Adquisición de una motoniveladora 0 Km</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>07-09-2026 09:00</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>id-051e57a55e616f48</t>
+          <t>id-61b6e4f9568150b0</t>
         </is>
       </c>
     </row>
@@ -776,14 +776,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CONCORDIA — MUNICIPALIDAD DE PUERTO YERUA</t>
+          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>1/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de una motoniveladora 0 Km</t>
+          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>id-61b6e4f9568150b0</t>
+          <t>id-85e6cfd11c8a8889</t>
         </is>
       </c>
     </row>
@@ -844,34 +844,34 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>77/2026</t>
+          <t>014/2026</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>ADQUISICION DE CAMIONETAS</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>11-09-2026 08:00</t>
+          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ) - SI ES DECRETADO INHABIL, AL DIA SIGUIENTE HABIL, A LA MISMA HORA Y LUGA</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -879,7 +879,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
+        </is>
+      </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -892,12 +896,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>id-dff70529581309e6</t>
+          <t>id-9e58cc9ec0b69356</t>
         </is>
       </c>
     </row>
@@ -912,14 +916,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -929,17 +933,17 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>27/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>14 de septiembre de 2026 - Hora: 10:00</t>
+          <t>16 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -965,7 +969,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>id-85e6cfd11c8a8889</t>
+          <t>id-608017f47f903d65</t>
         </is>
       </c>
     </row>
@@ -980,39 +984,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>MUNICIPALIDAD DE SEGUÍ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>76/2026</t>
+          <t>08-2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
+          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”. Apertura de Sobres 17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y entrega en Área de Suministro del Municipio, y también se podrá descargar en el Sitio Oficial Digital Municipal https://www.segui.gob.ar . Edgardo Muller, Presidente Municipal. ID:52321 - F.C. 04-00075716 3 v./03/09/2026</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>14-09-2026 08:00</t>
+          <t xml:space="preserve">17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y </t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr"/>
@@ -1028,12 +1032,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>id-ccdfae2a7ede4696</t>
+          <t>id-90c3d1f38f49418a</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1059,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1065,17 +1069,17 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>014/2026</t>
+          <t>015/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ) - SI ES DECRETADO INHABIL, AL DIA SIGUIENTE HABIL, A LA MISMA HORA Y LUGA</t>
+          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ) - SI ES DECRETADO INHABIL, AL DIA SIGUIENTE HABIL, A LA MISMA HORA Y LUGA</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -1085,7 +1089,7 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
+          <t>$ 90.000,00.- (PESOS NOVENTA MIL CON 00/100)</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -1105,7 +1109,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>id-9e58cc9ec0b69356</t>
+          <t>id-74dfdad7e5f9d048</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1131,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
+          <t>MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1135,19 +1139,15 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>27/2026</t>
-        </is>
-      </c>
+      <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>16 de septiembre de 2026 - Hora: 10:00</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -1155,7 +1155,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Sin Cargo</t>
+        </is>
+      </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1173,7 +1177,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>id-608017f47f903d65</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -1188,14 +1192,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SEGUÍ</t>
+          <t>MUNICIPIO — PRIMER LLAMADO A:</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1205,25 +1209,29 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>08-2026</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”. Apertura de Sobres 17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y entrega en Área de Suministro del Municipio, y también se podrá descargar en el Sitio Oficial Digital Municipal https://www.segui.gob.ar . Edgardo Muller, Presidente Municipal. ID:52321 - F.C. 04-00075716 3 v./03/09/2026</t>
+          <t>LUGAR DE APERTURA DE OFERTAS: – Oficina de Compras, Edificio Municipal, calle Juan D. Perón 232</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y </t>
+          <t>DE OFERTA: 07/09/2026 - 10 HS</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1241,7 +1249,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>id-90c3d1f38f49418a</t>
+          <t>id-56a815662b393a4b</t>
         </is>
       </c>
     </row>
@@ -1256,14 +1264,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>NOGOYA — COMUNA DISTRITO SAUCE -- NOGOYA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1273,17 +1281,17 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>015/2026</t>
+          <t>1/26</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
+          <t>Convocar para la adquisi ción de un Tractor agrícola 0 km, con las siguientes características técnicas: potencia de motor de 130 a 150 HP; doble Tracción, 6 (seis) cilindros; y demás especificación que se encuentran en el pliego de Especificaciones Técnicas</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ) - SI ES DECRETADO INHABIL, AL DIA SIGUIENTE HABIL, A LA MISMA HORA Y LUGA</t>
+          <t>DE PROPUESTAS: Día Viernes 11 de Septiembre de 2026- a las 10:00 horas en la Sede Comunal de Comuna Distrito Sauce</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1293,7 +1301,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>$ 90.000,00.- (PESOS NOVENTA MIL CON 00/100)</t>
+          <t xml:space="preserve">sin costo. Solicitar en la Sede Comunal de Distrito Sauce Nogoya o al </t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -1313,7 +1321,7 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>id-74dfdad7e5f9d048</t>
+          <t>id-328f5a2f67c14702</t>
         </is>
       </c>
     </row>
@@ -1328,14 +1336,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE COLON</t>
+          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1343,15 +1351,19 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>06/26</t>
+        </is>
+      </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1361,7 +1373,7 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>Sin Cargo</t>
+          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -1381,7 +1393,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-9dbdaa6090d92bd4</t>
         </is>
       </c>
     </row>
@@ -1396,14 +1408,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MUNICIPIO — PRIMER LLAMADO A:</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1413,17 +1425,17 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>LUGAR DE APERTURA DE OFERTAS: – Oficina de Compras, Edificio Municipal, calle Juan D. Perón 232</t>
+          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>DE OFERTA: 07/09/2026 - 10 HS</t>
+          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1431,29 +1443,21 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="J14" s="4" t="inlineStr"/>
       <c r="K14" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L14" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>id-56a815662b393a4b</t>
+          <t>id-952aef4c115d8f12</t>
         </is>
       </c>
     </row>
@@ -1468,14 +1472,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NOGOYA — COMUNA DISTRITO SAUCE -- NOGOYA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1485,17 +1489,17 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Convocar para la adquisi ción de un Tractor agrícola 0 km, con las siguientes características técnicas: potencia de motor de 130 a 150 HP; doble Tracción, 6 (seis) cilindros; y demás especificación que se encuentran en el pliego de Especificaciones Técnicas</t>
+          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>DE PROPUESTAS: Día Viernes 11 de Septiembre de 2026- a las 10:00 horas en la Sede Comunal de Comuna Distrito Sauce</t>
+          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1503,29 +1507,21 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sin costo. Solicitar en la Sede Comunal de Distrito Sauce Nogoya o al </t>
-        </is>
-      </c>
+      <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>id-328f5a2f67c14702</t>
+          <t>id-885d4847519dfd48</t>
         </is>
       </c>
     </row>
@@ -1535,19 +1531,19 @@
           <t>07/09/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
+          <t>MUNICIPIO DE ORO VERDE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1555,19 +1551,15 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>06/26</t>
-        </is>
-      </c>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
+          <t>El procedimiento licitatorio regido por el presente pliego tiene por objeto la Licitación Pública N° 03/2026 para la venta de los siguientes bienes municipales: a) MINI RETRO DE TIRO: Marca RICHIGER, Serie A, N° 101. Modelo N° 186. Motor N° 991023899, C. V 7, 50, Modelo 7, 50 DB, RPM 1.500 b) COLECTIVO: Mercedes Benz, dominio UKZ353, modelo 1977 según lo que s e detalla en el Pliego de Bases y Condiciones que forma parte de la presente como Anexo I</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
+          <t>La apertura de sobres se realizará el día 14 de septiembre del 2026 a las 10:00 horas, en la sede municipal</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1577,7 +1569,7 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
+          <t>El pliego será gratuito. El mismo se encontrará para su consulta y ent</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
@@ -1597,7 +1589,7 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>id-9dbdaa6090d92bd4</t>
+          <t>id-ddc4dfb118d357f7</t>
         </is>
       </c>
     </row>
@@ -1607,19 +1599,19 @@
           <t>07/09/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1629,17 +1621,17 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1656,12 +1648,12 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>id-952aef4c115d8f12</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
@@ -1671,19 +1663,19 @@
           <t>07/09/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1693,17 +1685,17 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1720,12 +1712,12 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>id-885d4847519dfd48</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -1740,14 +1732,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE ORO VERDE</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1755,15 +1747,19 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>03/2025</t>
+        </is>
+      </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>El procedimiento licitatorio regido por el presente pliego tiene por objeto la Licitación Pública N° 03/2026 para la venta de los siguientes bienes municipales: a) MINI RETRO DE TIRO: Marca RICHIGER, Serie A, N° 101. Modelo N° 186. Motor N° 991023899, C. V 7, 50, Modelo 7, 50 DB, RPM 1.500 b) COLECTIVO: Mercedes Benz, dominio UKZ353, modelo 1977 según lo que s e detalla en el Pliego de Bases y Condiciones que forma parte de la presente como Anexo I</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>La apertura de sobres se realizará el día 14 de septiembre del 2026 a las 10:00 horas, en la sede municipal</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1771,29 +1767,21 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>El pliego será gratuito. El mismo se encontrará para su consulta y ent</t>
-        </is>
-      </c>
+      <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L19" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>id-ddc4dfb118d357f7</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
@@ -1825,17 +1813,17 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -1857,7 +1845,7 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
@@ -1887,19 +1875,15 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1921,7 +1905,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
@@ -1953,17 +1937,17 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1985,7 +1969,7 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
@@ -2017,17 +2001,17 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -2049,7 +2033,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
@@ -2079,15 +2063,19 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -2109,7 +2097,7 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -2141,17 +2129,17 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>03/26</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -2173,7 +2161,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
@@ -2205,17 +2193,17 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -2237,7 +2225,7 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
@@ -2252,14 +2240,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2269,17 +2257,17 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -2287,21 +2275,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr"/>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>s in cargo Consultas: comprascomuna6to@hotmail.com Celular: 3444- 4493</t>
+        </is>
+      </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2323,27 +2319,27 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -2360,12 +2356,12 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -2380,14 +2376,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2397,17 +2393,17 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>04/2025</t>
+          <t>499/26</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -2424,12 +2420,12 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-f53eab44dba8d43f</t>
         </is>
       </c>
     </row>
@@ -2444,34 +2440,34 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>235/26</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>Licitación Privada N° 235/26: reparación de cenefas en losas pórticos</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -2479,29 +2475,21 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>s in cargo Consultas: comprascomuna6to@hotmail.com Celular: 3444- 4493</t>
-        </is>
-      </c>
+      <c r="J30" s="4" t="inlineStr"/>
       <c r="K30" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L30" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-22f9c51cdaebefb7</t>
         </is>
       </c>
     </row>
@@ -2516,29 +2504,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>498/26</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>LICITACIÓN PÚBLICA N° 498/26: reparación de un tramo del cerramiento perimetral del Túnel Subfluvial</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2560,12 +2548,12 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-46d81e3efd2ae483</t>
         </is>
       </c>
     </row>
@@ -2582,12 +2570,12 @@
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Áridos</t>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — Y PUESTA EN VALOR – ESCUE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2597,17 +2585,17 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>499/26</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t xml:space="preserve">de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN </t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -2615,21 +2603,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr"/>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Habilitación: Pesos Ciento Veinte Mil con 0/100 - $ 120.000, 00 - Habi</t>
+        </is>
+      </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>id-f53eab44dba8d43f</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
@@ -2644,34 +2640,34 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — TERMINACION ESCUELA Nº 54</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>235/26</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Licitación Privada N° 235/26: reparación de cenefas en losas pórticos</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez realizado el depósito/transferenci</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN N</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -2679,234 +2675,34 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>Habilitación: Pesos Ochenta Mil con 0/100 - $ 80.000, 00 - Habilitació</t>
+        </is>
+      </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>id-22f9c51cdaebefb7</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>07/09/2026</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Túnel Subfluvial</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>498/26</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>LICITACIÓN PÚBLICA N° 498/26: reparación de un tramo del cerramiento perimetral del Túnel Subfluvial</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr"/>
-      <c r="K34" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Túnel Subfluvial</t>
-        </is>
-      </c>
-      <c r="N34" s="4" t="inlineStr">
-        <is>
-          <t>id-46d81e3efd2ae483</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>07/09/2026</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — Y PUESTA EN VALOR – ESCUE</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>09/2026</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN </t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>Habilitación: Pesos Ciento Veinte Mil con 0/100 - $ 120.000, 00 - Habi</t>
-        </is>
-      </c>
-      <c r="K35" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L35" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Boletín Oficial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="N35" s="4" t="inlineStr">
-        <is>
-          <t>id-f8fab7a7b3a06a2d</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>07/09/2026</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — TERMINACION ESCUELA Nº 54</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>10/2026</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez realizado el depósito/transferenci</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN N</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>Habilitación: Pesos Ochenta Mil con 0/100 - $ 80.000, 00 - Habilitació</t>
-        </is>
-      </c>
-      <c r="K36" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L36" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Boletín Oficial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="N36" s="4" t="inlineStr">
-        <is>
           <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N36"/>
+  <autoFilter ref="A1:N33"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -2933,35 +2729,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$N$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$N$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -776,34 +776,34 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>77/2026</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>ADQUISICION DE CAMIONETAS</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>14 de septiembre de 2026 - Hora: 10:00</t>
+          <t>11-09-2026 08:00</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>id-85e6cfd11c8a8889</t>
+          <t>id-dff70529581309e6</t>
         </is>
       </c>
     </row>
@@ -844,14 +844,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
+          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -861,17 +861,17 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>014/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
+          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ) - SI ES DECRETADO INHABIL, AL DIA SIGUIENTE HABIL, A LA MISMA HORA Y LUGA</t>
+          <t>14 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -879,11 +879,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
-        </is>
-      </c>
+      <c r="J6" s="4" t="inlineStr"/>
       <c r="K6" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -901,7 +897,7 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>id-9e58cc9ec0b69356</t>
+          <t>id-85e6cfd11c8a8889</t>
         </is>
       </c>
     </row>
@@ -916,34 +912,34 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>27/2026</t>
+          <t>76/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
+          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>16 de septiembre de 2026 - Hora: 10:00</t>
+          <t>14-09-2026 08:00</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -964,12 +960,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>id-608017f47f903d65</t>
+          <t>id-ccdfae2a7ede4696</t>
         </is>
       </c>
     </row>
@@ -984,14 +980,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SEGUÍ</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1001,25 +997,29 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>08-2026</t>
+          <t>014/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”. Apertura de Sobres 17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y entrega en Área de Suministro del Municipio, y también se podrá descargar en el Sitio Oficial Digital Municipal https://www.segui.gob.ar . Edgardo Muller, Presidente Municipal. ID:52321 - F.C. 04-00075716 3 v./03/09/2026</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y </t>
+          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ) - SI ES DECRETADO INHABIL, AL DIA SIGUIENTE HABIL, A LA MISMA HORA Y LUGA</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
+        </is>
+      </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>id-90c3d1f38f49418a</t>
+          <t>id-9e58cc9ec0b69356</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>015/2026</t>
+          <t>27/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
+          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ) - SI ES DECRETADO INHABIL, AL DIA SIGUIENTE HABIL, A LA MISMA HORA Y LUGA</t>
+          <t>16 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -1087,11 +1087,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>$ 90.000,00.- (PESOS NOVENTA MIL CON 00/100)</t>
-        </is>
-      </c>
+      <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1109,7 +1105,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>id-74dfdad7e5f9d048</t>
+          <t>id-608017f47f903d65</t>
         </is>
       </c>
     </row>
@@ -1124,14 +1120,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE COLON</t>
+          <t>MUNICIPALIDAD DE SEGUÍ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1139,27 +1135,27 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>08-2026</t>
+        </is>
+      </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”. Apertura de Sobres 17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y entrega en Área de Suministro del Municipio, y también se podrá descargar en el Sitio Oficial Digital Municipal https://www.segui.gob.ar . Edgardo Muller, Presidente Municipal. ID:52321 - F.C. 04-00075716 3 v./03/09/2026</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t xml:space="preserve">17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y </t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>Sin Cargo</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr"/>
       <c r="K10" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1177,7 +1173,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-90c3d1f38f49418a</t>
         </is>
       </c>
     </row>
@@ -1192,14 +1188,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MUNICIPIO — PRIMER LLAMADO A:</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1209,17 +1205,17 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>015/2026</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>LUGAR DE APERTURA DE OFERTAS: – Oficina de Compras, Edificio Municipal, calle Juan D. Perón 232</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>DE OFERTA: 07/09/2026 - 10 HS</t>
+          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ) - SI ES DECRETADO INHABIL, AL DIA SIGUIENTE HABIL, A LA MISMA HORA Y LUGA</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -1229,7 +1225,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$ 90.000,00.- (PESOS NOVENTA MIL CON 00/100)</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -1249,7 +1245,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>id-56a815662b393a4b</t>
+          <t>id-74dfdad7e5f9d048</t>
         </is>
       </c>
     </row>
@@ -1264,14 +1260,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NOGOYA — COMUNA DISTRITO SAUCE -- NOGOYA</t>
+          <t>MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1279,19 +1275,15 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1/26</t>
-        </is>
-      </c>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Convocar para la adquisi ción de un Tractor agrícola 0 km, con las siguientes características técnicas: potencia de motor de 130 a 150 HP; doble Tracción, 6 (seis) cilindros; y demás especificación que se encuentran en el pliego de Especificaciones Técnicas</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>DE PROPUESTAS: Día Viernes 11 de Septiembre de 2026- a las 10:00 horas en la Sede Comunal de Comuna Distrito Sauce</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1301,7 +1293,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sin costo. Solicitar en la Sede Comunal de Distrito Sauce Nogoya o al </t>
+          <t>Sin Cargo</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -1321,7 +1313,7 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>id-328f5a2f67c14702</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1335,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
+          <t>MUNICIPIO — PRIMER LLAMADO A:</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1353,17 +1345,17 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>06/26</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
+          <t>LUGAR DE APERTURA DE OFERTAS: – Oficina de Compras, Edificio Municipal, calle Juan D. Perón 232</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
+          <t>DE OFERTA: 07/09/2026 - 10 HS</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1373,7 +1365,7 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -1393,7 +1385,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>id-9dbdaa6090d92bd4</t>
+          <t>id-56a815662b393a4b</t>
         </is>
       </c>
     </row>
@@ -1408,14 +1400,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>NOGOYA — COMUNA DISTRITO SAUCE -- NOGOYA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1425,17 +1417,17 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>1/26</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
+          <t>Convocar para la adquisi ción de un Tractor agrícola 0 km, con las siguientes características técnicas: potencia de motor de 130 a 150 HP; doble Tracción, 6 (seis) cilindros; y demás especificación que se encuentran en el pliego de Especificaciones Técnicas</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
+          <t>DE PROPUESTAS: Día Viernes 11 de Septiembre de 2026- a las 10:00 horas en la Sede Comunal de Comuna Distrito Sauce</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1443,21 +1435,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sin costo. Solicitar en la Sede Comunal de Distrito Sauce Nogoya o al </t>
+        </is>
+      </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>id-952aef4c115d8f12</t>
+          <t>id-328f5a2f67c14702</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1489,17 +1489,17 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>06/26</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1507,21 +1507,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
+        </is>
+      </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>id-885d4847519dfd48</t>
+          <t>id-9dbdaa6090d92bd4</t>
         </is>
       </c>
     </row>
@@ -1531,19 +1539,19 @@
           <t>07/09/2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE ORO VERDE</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1551,15 +1559,19 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>08/2026</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>El procedimiento licitatorio regido por el presente pliego tiene por objeto la Licitación Pública N° 03/2026 para la venta de los siguientes bienes municipales: a) MINI RETRO DE TIRO: Marca RICHIGER, Serie A, N° 101. Modelo N° 186. Motor N° 991023899, C. V 7, 50, Modelo 7, 50 DB, RPM 1.500 b) COLECTIVO: Mercedes Benz, dominio UKZ353, modelo 1977 según lo que s e detalla en el Pliego de Bases y Condiciones que forma parte de la presente como Anexo I</t>
+          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>La apertura de sobres se realizará el día 14 de septiembre del 2026 a las 10:00 horas, en la sede municipal</t>
+          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1567,29 +1579,21 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>El pliego será gratuito. El mismo se encontrará para su consulta y ent</t>
-        </is>
-      </c>
+      <c r="J16" s="4" t="inlineStr"/>
       <c r="K16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>id-ddc4dfb118d357f7</t>
+          <t>id-952aef4c115d8f12</t>
         </is>
       </c>
     </row>
@@ -1599,19 +1603,19 @@
           <t>07/09/2026</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1621,17 +1625,17 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1648,12 +1652,12 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-885d4847519dfd48</t>
         </is>
       </c>
     </row>
@@ -1668,14 +1672,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>MUNICIPIO DE ORO VERDE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1683,19 +1687,15 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>El procedimiento licitatorio regido por el presente pliego tiene por objeto la Licitación Pública N° 03/2026 para la venta de los siguientes bienes municipales: a) MINI RETRO DE TIRO: Marca RICHIGER, Serie A, N° 101. Modelo N° 186. Motor N° 991023899, C. V 7, 50, Modelo 7, 50 DB, RPM 1.500 b) COLECTIVO: Mercedes Benz, dominio UKZ353, modelo 1977 según lo que s e detalla en el Pliego de Bases y Condiciones que forma parte de la presente como Anexo I</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>La apertura de sobres se realizará el día 14 de septiembre del 2026 a las 10:00 horas, en la sede municipal</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1703,21 +1703,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr"/>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>El pliego será gratuito. El mismo se encontrará para su consulta y ent</t>
+        </is>
+      </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-ddc4dfb118d357f7</t>
         </is>
       </c>
     </row>
@@ -1749,17 +1757,17 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1781,7 +1789,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
@@ -1813,17 +1821,17 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -1845,7 +1853,7 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -1875,15 +1883,19 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>03/2025</t>
+        </is>
+      </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1905,7 +1917,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
@@ -1937,17 +1949,17 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1969,7 +1981,7 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
@@ -1999,19 +2011,15 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>06/2025</t>
-        </is>
-      </c>
+      <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -2033,7 +2041,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
@@ -2065,17 +2073,17 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -2097,7 +2105,7 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
@@ -2129,17 +2137,17 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -2161,7 +2169,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
@@ -2193,17 +2201,17 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>04/2025</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -2225,7 +2233,7 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -2240,14 +2248,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2257,17 +2265,17 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>03/26</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -2275,29 +2283,21 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>s in cargo Consultas: comprascomuna6to@hotmail.com Celular: 3444- 4493</t>
-        </is>
-      </c>
+      <c r="J27" s="4" t="inlineStr"/>
       <c r="K27" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L27" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
@@ -2319,27 +2319,27 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -2356,12 +2356,12 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
@@ -2376,14 +2376,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>499/26</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -2411,21 +2411,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr"/>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>s in cargo Consultas: comprascomuna6to@hotmail.com Celular: 3444- 4493</t>
+        </is>
+      </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>id-f53eab44dba8d43f</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2440,29 +2448,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>235/26</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Licitación Privada N° 235/26: reparación de cenefas en losas pórticos</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2484,12 +2492,12 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>id-22f9c51cdaebefb7</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -2504,9 +2512,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2521,12 +2529,12 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>498/26</t>
+          <t>499/26</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA N° 498/26: reparación de un tramo del cerramiento perimetral del Túnel Subfluvial</t>
+          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2553,7 +2561,7 @@
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>id-46d81e3efd2ae483</t>
+          <t>id-f53eab44dba8d43f</t>
         </is>
       </c>
     </row>
@@ -2575,27 +2583,27 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — Y PUESTA EN VALOR – ESCUE</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>235/26</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez</t>
+          <t>Licitación Privada N° 235/26: reparación de cenefas en losas pórticos</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN </t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -2603,29 +2611,21 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>Habilitación: Pesos Ciento Veinte Mil con 0/100 - $ 120.000, 00 - Habi</t>
-        </is>
-      </c>
+      <c r="J32" s="4" t="inlineStr"/>
       <c r="K32" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L32" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-22f9c51cdaebefb7</t>
         </is>
       </c>
     </row>
@@ -2647,62 +2647,198 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>Túnel Subfluvial</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>498/26</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>LICITACIÓN PÚBLICA N° 498/26: reparación de un tramo del cerramiento perimetral del Túnel Subfluvial</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr"/>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Túnel Subfluvial</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>id-46d81e3efd2ae483</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — Y PUESTA EN VALOR – ESCUE</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>09/2026</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN </t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Habilitación: Pesos Ciento Veinte Mil con 0/100 - $ 120.000, 00 - Habi</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Boletín Oficial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>id-f8fab7a7b3a06a2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — TERMINACION ESCUELA Nº 54</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>10/2026</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez realizado el depósito/transferenci</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN N</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>Habilitación: Pesos Ochenta Mil con 0/100 - $ 80.000, 00 - Habilitació</t>
         </is>
       </c>
-      <c r="K33" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L33" s="6" t="inlineStr">
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N33"/>
+  <autoFilter ref="A1:N35"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -2729,29 +2865,33 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$N$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$N$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -62,12 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -640,34 +640,34 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SAN JOSÉ</t>
+          <t>CONCORDIA — MUNICIPALIDAD DE PUERTO YERUA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>1/2026</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>selección de proveedor/es para la adquisición de materiales con destino a la realización de cordón cuneta y badenes de la calle Urquiza entre calles Pueyrredón e Independencia</t>
+          <t>Adquisición de una motoniveladora 0 Km</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>07 de septiembre de 2026 a las 09:00 hs</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>id-2b7062803859510f</t>
+          <t>id-61b6e4f9568150b0</t>
         </is>
       </c>
     </row>
@@ -715,27 +715,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CONCORDIA — MUNICIPALIDAD DE PUERTO YERUA</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1/2026</t>
+          <t>77/2026</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de una motoniveladora 0 Km</t>
+          <t>ADQUISICION DE CAMIONETAS</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11-09-2026 08:00</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>id-61b6e4f9568150b0</t>
+          <t>id-dff70529581309e6</t>
         </is>
       </c>
     </row>
@@ -776,34 +776,34 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>77/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>ADQUISICION DE CAMIONETAS</t>
+          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>11-09-2026 08:00</t>
+          <t>14 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>id-dff70529581309e6</t>
+          <t>id-85e6cfd11c8a8889</t>
         </is>
       </c>
     </row>
@@ -844,34 +844,34 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>76/2026</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>14 de septiembre de 2026 - Hora: 10:00</t>
+          <t>14-09-2026 08:00</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -892,12 +892,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>id-85e6cfd11c8a8889</t>
+          <t>id-ccdfae2a7ede4696</t>
         </is>
       </c>
     </row>
@@ -912,34 +912,34 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>76/2026</t>
+          <t>014/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>14-09-2026 08:00</t>
+          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ) - SI ES DECRETADO INHABIL, AL DIA SIGUIENTE HABIL, A LA MISMA HORA Y LUGA</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -947,7 +947,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
+        </is>
+      </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -960,12 +964,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>id-ccdfae2a7ede4696</t>
+          <t>id-9e58cc9ec0b69356</t>
         </is>
       </c>
     </row>
@@ -980,14 +984,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -997,17 +1001,17 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>014/2026</t>
+          <t>27/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
+          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ) - SI ES DECRETADO INHABIL, AL DIA SIGUIENTE HABIL, A LA MISMA HORA Y LUGA</t>
+          <t>16 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -1015,11 +1019,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
-        </is>
-      </c>
+      <c r="J8" s="4" t="inlineStr"/>
       <c r="K8" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>id-9e58cc9ec0b69356</t>
+          <t>id-608017f47f903d65</t>
         </is>
       </c>
     </row>
@@ -1052,14 +1052,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
+          <t>MUNICIPALIDAD DE SEGUÍ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1069,22 +1069,22 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>27/2026</t>
+          <t>08-2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
+          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”. Apertura de Sobres 17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y entrega en Área de Suministro del Municipio, y también se podrá descargar en el Sitio Oficial Digital Municipal https://www.segui.gob.ar . Edgardo Muller, Presidente Municipal. ID:52321 - F.C. 04-00075716 3 v./03/09/2026</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>16 de septiembre de 2026 - Hora: 10:00</t>
+          <t xml:space="preserve">17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y </t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>id-608017f47f903d65</t>
+          <t>id-90c3d1f38f49418a</t>
         </is>
       </c>
     </row>
@@ -1120,14 +1120,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SEGUÍ</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1137,25 +1137,29 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>08-2026</t>
+          <t>015/2026</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”. Apertura de Sobres 17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y entrega en Área de Suministro del Municipio, y también se podrá descargar en el Sitio Oficial Digital Municipal https://www.segui.gob.ar . Edgardo Muller, Presidente Municipal. ID:52321 - F.C. 04-00075716 3 v./03/09/2026</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y </t>
+          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ) - SI ES DECRETADO INHABIL, AL DIA SIGUIENTE HABIL, A LA MISMA HORA Y LUGA</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
+        </is>
+      </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1173,7 +1177,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>id-90c3d1f38f49418a</t>
+          <t>id-74dfdad7e5f9d048</t>
         </is>
       </c>
     </row>
@@ -1188,14 +1192,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1203,19 +1207,15 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>015/2026</t>
-        </is>
-      </c>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ) - SI ES DECRETADO INHABIL, AL DIA SIGUIENTE HABIL, A LA MISMA HORA Y LUGA</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>$ 90.000,00.- (PESOS NOVENTA MIL CON 00/100)</t>
+          <t>Sin Cargo</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>id-74dfdad7e5f9d048</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -1260,14 +1260,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE COLON</t>
+          <t>NOGOYA — COMUNA DISTRITO SAUCE -- NOGOYA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1275,15 +1275,19 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1/26</t>
+        </is>
+      </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>Convocar para la adquisi ción de un Tractor agrícola 0 km, con las siguientes características técnicas: potencia de motor de 130 a 150 HP; doble Tracción, 6 (seis) cilindros; y demás especificación que se encuentran en el pliego de Especificaciones Técnicas</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>DE PROPUESTAS: Día Viernes 11 de Septiembre de 2026- a las 10:00 horas en la Sede Comunal de Comuna Distrito Sauce</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1293,7 +1297,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Sin Cargo</t>
+          <t xml:space="preserve">sin costo. Solicitar en la Sede Comunal de Distrito Sauce Nogoya o al </t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -1313,7 +1317,7 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-328f5a2f67c14702</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1339,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MUNICIPIO — PRIMER LLAMADO A:</t>
+          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1345,17 +1349,17 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>06/26</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>LUGAR DE APERTURA DE OFERTAS: – Oficina de Compras, Edificio Municipal, calle Juan D. Perón 232</t>
+          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>DE OFERTA: 07/09/2026 - 10 HS</t>
+          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1365,7 +1369,7 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -1385,7 +1389,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>id-56a815662b393a4b</t>
+          <t>id-9dbdaa6090d92bd4</t>
         </is>
       </c>
     </row>
@@ -1400,14 +1404,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NOGOYA — COMUNA DISTRITO SAUCE -- NOGOYA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1417,17 +1421,17 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Convocar para la adquisi ción de un Tractor agrícola 0 km, con las siguientes características técnicas: potencia de motor de 130 a 150 HP; doble Tracción, 6 (seis) cilindros; y demás especificación que se encuentran en el pliego de Especificaciones Técnicas</t>
+          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>DE PROPUESTAS: Día Viernes 11 de Septiembre de 2026- a las 10:00 horas en la Sede Comunal de Comuna Distrito Sauce</t>
+          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1435,29 +1439,21 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sin costo. Solicitar en la Sede Comunal de Distrito Sauce Nogoya o al </t>
-        </is>
-      </c>
+      <c r="J14" s="4" t="inlineStr"/>
       <c r="K14" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L14" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>id-328f5a2f67c14702</t>
+          <t>id-952aef4c115d8f12</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1475,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1489,17 +1485,17 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>06/26</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
+          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
+          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1507,41 +1503,33 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
-        </is>
-      </c>
+      <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>id-9dbdaa6090d92bd4</t>
+          <t>id-885d4847519dfd48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -1551,7 +1539,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1561,17 +1549,17 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
+          <t>DE PROPUESTAS: Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1579,21 +1567,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr"/>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>id-952aef4c115d8f12</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -1603,19 +1599,19 @@
           <t>07/09/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>MUNICIPIO DE ORO VERDE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1623,19 +1619,15 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>09/2026</t>
-        </is>
-      </c>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>El procedimiento licitatorio regido por el presente pliego tiene por objeto la Licitación Pública N° 03/2026 para la venta de los siguientes bienes municipales: a) MINI RETRO DE TIRO: Marca RICHIGER, Serie A, N° 101. Modelo N° 186. Motor N° 991023899, C. V 7, 50, Modelo 7, 50 DB, RPM 1.500 b) COLECTIVO: Mercedes Benz, dominio UKZ353, modelo 1977 según lo que s e detalla en el Pliego de Bases y Condiciones que forma parte de la presente como Anexo I</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>La apertura de sobres se realizará el día 14 de septiembre del 2026 a las 10:00 horas, en la sede municipal</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1643,21 +1635,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr"/>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>El pliego será gratuito. El mismo se encontrará para su consulta y ent</t>
+        </is>
+      </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>id-885d4847519dfd48</t>
+          <t>id-ddc4dfb118d357f7</t>
         </is>
       </c>
     </row>
@@ -1672,14 +1672,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE ORO VERDE</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1687,15 +1687,19 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>01/2026</t>
+        </is>
+      </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>El procedimiento licitatorio regido por el presente pliego tiene por objeto la Licitación Pública N° 03/2026 para la venta de los siguientes bienes municipales: a) MINI RETRO DE TIRO: Marca RICHIGER, Serie A, N° 101. Modelo N° 186. Motor N° 991023899, C. V 7, 50, Modelo 7, 50 DB, RPM 1.500 b) COLECTIVO: Mercedes Benz, dominio UKZ353, modelo 1977 según lo que s e detalla en el Pliego de Bases y Condiciones que forma parte de la presente como Anexo I</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>La apertura de sobres se realizará el día 14 de septiembre del 2026 a las 10:00 horas, en la sede municipal</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1703,29 +1707,21 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>El pliego será gratuito. El mismo se encontrará para su consulta y ent</t>
-        </is>
-      </c>
+      <c r="J18" s="4" t="inlineStr"/>
       <c r="K18" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L18" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>id-ddc4dfb118d357f7</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1736,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -1757,17 +1753,17 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1789,7 +1785,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1800,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -1821,17 +1817,17 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -1853,7 +1849,7 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1864,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -1885,17 +1881,17 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1917,7 +1913,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1928,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -1947,19 +1943,15 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>02/2026</t>
-        </is>
-      </c>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1981,7 +1973,7 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1988,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2011,15 +2003,19 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>05/2025</t>
+        </is>
+      </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -2041,7 +2037,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2052,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2073,17 +2069,17 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -2105,7 +2101,7 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2116,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2137,17 +2133,17 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -2169,7 +2165,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2180,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2201,17 +2197,17 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>03/26</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -2233,7 +2229,7 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2244,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2265,17 +2261,17 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -2297,7 +2293,7 @@
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
@@ -2312,14 +2308,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2329,17 +2325,17 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>04/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -2347,21 +2343,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr"/>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>s in cargo Consultas: comprascomuna6to@hotmail.com Celular: 3444- 4493</t>
+        </is>
+      </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2376,34 +2380,34 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -2411,29 +2415,21 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>s in cargo Consultas: comprascomuna6to@hotmail.com Celular: 3444- 4493</t>
-        </is>
-      </c>
+      <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L29" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -2450,27 +2446,27 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>499/26</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2492,12 +2488,12 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-f53eab44dba8d43f</t>
         </is>
       </c>
     </row>
@@ -2512,9 +2508,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2524,17 +2520,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>499/26</t>
+          <t>235/26</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
+          <t>Licitación Privada N° 235/26: reparación de cenefas en losas pórticos</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2561,7 +2557,7 @@
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>id-f53eab44dba8d43f</t>
+          <t>id-22f9c51cdaebefb7</t>
         </is>
       </c>
     </row>
@@ -2588,17 +2584,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>235/26</t>
+          <t>498/26</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Licitación Privada N° 235/26: reparación de cenefas en losas pórticos</t>
+          <t>LICITACIÓN PÚBLICA N° 498/26: reparación de un tramo del cerramiento perimetral del Túnel Subfluvial</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2625,7 +2621,7 @@
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>id-22f9c51cdaebefb7</t>
+          <t>id-46d81e3efd2ae483</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2643,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — Y PUESTA EN VALOR – ESCUE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2657,17 +2653,17 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>498/26</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA N° 498/26: reparación de un tramo del cerramiento perimetral del Túnel Subfluvial</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t xml:space="preserve">de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN </t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -2675,21 +2671,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>Habilitación: Pesos Ciento Veinte Mil con 0/100 - $ 120.000, 00 - Habi</t>
+        </is>
+      </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>id-46d81e3efd2ae483</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2715,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — Y PUESTA EN VALOR – ESCUE</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — TERMINACION ESCUELA Nº 54</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2721,17 +2725,17 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez realizado el depósito/transferenci</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN </t>
+          <t>de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN N</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2741,7 +2745,7 @@
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>Habilitación: Pesos Ciento Veinte Mil con 0/100 - $ 120.000, 00 - Habi</t>
+          <t>Habilitación: Pesos Ochenta Mil con 0/100 - $ 80.000, 00 - Habilitació</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
@@ -2761,84 +2765,12 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>07/09/2026</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — TERMINACION ESCUELA Nº 54</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>10/2026</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez realizado el depósito/transferenci</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN N</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>Habilitación: Pesos Ochenta Mil con 0/100 - $ 80.000, 00 - Habilitació</t>
-        </is>
-      </c>
-      <c r="K35" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L35" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Boletín Oficial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="N35" s="4" t="inlineStr">
-        <is>
           <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N35"/>
+  <autoFilter ref="A1:N34"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -2865,33 +2797,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$N$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$N$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1252,7 +1252,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1260,14 +1260,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NOGOYA — COMUNA DISTRITO SAUCE -- NOGOYA</t>
+          <t>CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ — CONDARCO”</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Convocar para la adquisi ción de un Tractor agrícola 0 km, con las siguientes características técnicas: potencia de motor de 130 a 150 HP; doble Tracción, 6 (seis) cilindros; y demás especificación que se encuentran en el pliego de Especificaciones Técnicas</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>DE PROPUESTAS: Día Viernes 11 de Septiembre de 2026- a las 10:00 horas en la Sede Comunal de Comuna Distrito Sauce</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sin costo. Solicitar en la Sede Comunal de Distrito Sauce Nogoya o al </t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>id-328f5a2f67c14702</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -1332,14 +1332,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
+          <t>NOGOYA — COMUNA DISTRITO SAUCE -- NOGOYA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1349,17 +1349,17 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>06/26</t>
+          <t>1/26</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
+          <t>Convocar para la adquisi ción de un Tractor agrícola 0 km, con las siguientes características técnicas: potencia de motor de 130 a 150 HP; doble Tracción, 6 (seis) cilindros; y demás especificación que se encuentran en el pliego de Especificaciones Técnicas</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
+          <t>DE PROPUESTAS: Día Viernes 11 de Septiembre de 2026- a las 10:00 horas en la Sede Comunal de Comuna Distrito Sauce</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
+          <t xml:space="preserve">sin costo. Solicitar en la Sede Comunal de Distrito Sauce Nogoya o al </t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>id-9dbdaa6090d92bd4</t>
+          <t>id-328f5a2f67c14702</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>06/26</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
+          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
+          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1439,21 +1439,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
+        </is>
+      </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>id-952aef4c115d8f12</t>
+          <t>id-9dbdaa6090d92bd4</t>
         </is>
       </c>
     </row>
@@ -1485,17 +1493,17 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1517,7 +1525,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>id-885d4847519dfd48</t>
+          <t>id-952aef4c115d8f12</t>
         </is>
       </c>
     </row>
@@ -1527,9 +1535,9 @@
           <t>08/09/2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -1539,7 +1547,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1549,17 +1557,17 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>DE PROPUESTAS: Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1567,29 +1575,21 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="J16" s="4" t="inlineStr"/>
       <c r="K16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
@@ -1599,19 +1599,19 @@
           <t>07/09/2026</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE ORO VERDE</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1619,15 +1619,19 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>09/2026</t>
+        </is>
+      </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>El procedimiento licitatorio regido por el presente pliego tiene por objeto la Licitación Pública N° 03/2026 para la venta de los siguientes bienes municipales: a) MINI RETRO DE TIRO: Marca RICHIGER, Serie A, N° 101. Modelo N° 186. Motor N° 991023899, C. V 7, 50, Modelo 7, 50 DB, RPM 1.500 b) COLECTIVO: Mercedes Benz, dominio UKZ353, modelo 1977 según lo que s e detalla en el Pliego de Bases y Condiciones que forma parte de la presente como Anexo I</t>
+          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>La apertura de sobres se realizará el día 14 de septiembre del 2026 a las 10:00 horas, en la sede municipal</t>
+          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1635,29 +1639,21 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>El pliego será gratuito. El mismo se encontrará para su consulta y ent</t>
-        </is>
-      </c>
+      <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>id-ddc4dfb118d357f7</t>
+          <t>id-885d4847519dfd48</t>
         </is>
       </c>
     </row>
@@ -1672,14 +1668,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>MUNICIPIO DE ORO VERDE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1687,19 +1683,15 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>01/2026</t>
-        </is>
-      </c>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>El procedimiento licitatorio regido por el presente pliego tiene por objeto la Licitación Pública N° 03/2026 para la venta de los siguientes bienes municipales: a) MINI RETRO DE TIRO: Marca RICHIGER, Serie A, N° 101. Modelo N° 186. Motor N° 991023899, C. V 7, 50, Modelo 7, 50 DB, RPM 1.500 b) COLECTIVO: Mercedes Benz, dominio UKZ353, modelo 1977 según lo que s e detalla en el Pliego de Bases y Condiciones que forma parte de la presente como Anexo I</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>La apertura de sobres se realizará el día 14 de septiembre del 2026 a las 10:00 horas, en la sede municipal</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1707,21 +1699,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr"/>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>El pliego será gratuito. El mismo se encontrará para su consulta y ent</t>
+        </is>
+      </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-ddc4dfb118d357f7</t>
         </is>
       </c>
     </row>
@@ -1753,17 +1753,17 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
@@ -1817,17 +1817,17 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -1881,17 +1881,17 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
@@ -1943,15 +1943,19 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>02/2026</t>
+        </is>
+      </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1973,7 +1977,7 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
@@ -2003,19 +2007,15 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>05/2025</t>
-        </is>
-      </c>
+      <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
@@ -2069,17 +2069,17 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
@@ -2133,17 +2133,17 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
@@ -2197,17 +2197,17 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -2261,17 +2261,17 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>04/2025</t>
+          <t>03/26</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
@@ -2308,14 +2308,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -2343,36 +2343,28 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>s in cargo Consultas: comprascomuna6to@hotmail.com Celular: 3444- 4493</t>
-        </is>
-      </c>
+      <c r="J28" s="4" t="inlineStr"/>
       <c r="K28" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L28" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2380,34 +2372,34 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>L LAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -2415,21 +2407,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr"/>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2444,14 +2444,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2461,17 +2461,17 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>499/26</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -2479,21 +2479,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr"/>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>s in cargo Consultas: comprascomuna6to@hotmail.com Celular: 3444- 4493</t>
+        </is>
+      </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>id-f53eab44dba8d43f</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2508,29 +2516,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>235/26</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Licitación Privada N° 235/26: reparación de cenefas en losas pórticos</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2552,12 +2560,12 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>id-22f9c51cdaebefb7</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -2572,9 +2580,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2589,12 +2597,12 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>498/26</t>
+          <t>499/26</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA N° 498/26: reparación de un tramo del cerramiento perimetral del Túnel Subfluvial</t>
+          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2621,7 +2629,7 @@
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>id-46d81e3efd2ae483</t>
+          <t>id-f53eab44dba8d43f</t>
         </is>
       </c>
     </row>
@@ -2643,27 +2651,27 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — Y PUESTA EN VALOR – ESCUE</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>235/26</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez</t>
+          <t>Licitación Privada N° 235/26: reparación de cenefas en losas pórticos</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN </t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -2671,29 +2679,21 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>Habilitación: Pesos Ciento Veinte Mil con 0/100 - $ 120.000, 00 - Habi</t>
-        </is>
-      </c>
+      <c r="J33" s="4" t="inlineStr"/>
       <c r="K33" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="L33" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-22f9c51cdaebefb7</t>
         </is>
       </c>
     </row>
@@ -2715,62 +2715,198 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>Túnel Subfluvial</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>498/26</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>LICITACIÓN PÚBLICA N° 498/26: reparación de un tramo del cerramiento perimetral del Túnel Subfluvial</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr"/>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Túnel Subfluvial</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>id-46d81e3efd2ae483</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — Y PUESTA EN VALOR – ESCUE</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>09/2026</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN </t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Habilitación: Pesos Ciento Veinte Mil con 0/100 - $ 120.000, 00 - Habi</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Boletín Oficial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>id-f8fab7a7b3a06a2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — TERMINACION ESCUELA Nº 54</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>10/2026</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez realizado el depósito/transferenci</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN N</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>Habilitación: Pesos Ochenta Mil con 0/100 - $ 80.000, 00 - Habilitació</t>
         </is>
       </c>
-      <c r="K34" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L34" s="6" t="inlineStr">
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="N36" s="4" t="inlineStr">
         <is>
           <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N34"/>
+  <autoFilter ref="A1:N36"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
@@ -2797,12 +2933,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId34"/>
@@ -2813,15 +2949,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$N$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -476,13 +476,14 @@
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="70" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-    <col hidden="1" width="1" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col hidden="1" width="1" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -528,30 +529,35 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Detalle apertura</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Venta hasta</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Valor pliego</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Pliego PDF</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
@@ -560,7 +566,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -595,35 +601,40 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
           <t>01 de OCTUBRE de 2026 a la hora 10:00 en la Oficina de Compras de la Municipalidad de Villa Elisa, Entre Ríos</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">$ 20.000,00 (Pesos Veinte mil con 00/100) el que se puede adquirir en </t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
       <c r="L2" s="6" t="inlineStr">
         <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>id-0132097e777a3442</t>
         </is>
@@ -632,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -672,26 +683,31 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr"/>
       <c r="L3" s="6" t="inlineStr">
         <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>id-61b6e4f9568150b0</t>
         </is>
@@ -700,7 +716,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -715,60 +731,69 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>NOGOYA — COMUNA DISTRITO SAUCE -- NOGOYA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>77/2026</t>
+          <t>1/26</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>ADQUISICION DE CAMIONETAS</t>
+          <t>Convocar para la adquisi ción de un Tractor agrícola 0 km, con las siguientes características técnicas: potencia de motor de 130 a 150 HP; doble Tracción, 6 (seis) cilindros; y demás especificación que se encuentran en el pliego de Especificaciones Técnicas</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>11-09-2026 08:00</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
+          <t>Viernes 11 de Septiembre de 2026- a las 10:00 horas en la Sede Comunal de Comuna Distrito Sauce</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sin costo. Solicitar en la Sede Comunal de Distrito Sauce Nogoya o al </t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Municipalidad de Paraná</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>id-dff70529581309e6</t>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Boletín Oficial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>id-328f5a2f67c14702</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -776,67 +801,72 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>77/2026</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>ADQUISICION DE CAMIONETAS</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>14 de septiembre de 2026 - Hora: 10:00</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
+          <t>11-09-2026 08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr"/>
       <c r="L5" s="6" t="inlineStr">
         <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Boletín Oficial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>id-85e6cfd11c8a8889</t>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Municipalidad de Paraná</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>id-dff70529581309e6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -844,67 +874,72 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>76/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
+          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>14-09-2026 08:00</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
+          <t>14 de septiembre de 2026 - Hora: 10:00</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="6" t="inlineStr">
         <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Municipalidad de Paraná</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>id-ccdfae2a7ede4696</t>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Boletín Oficial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>id-85e6cfd11c8a8889</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -912,14 +947,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
+          <t>MUNICIPIO DE ORO VERDE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -927,56 +962,57 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>014/2026</t>
-        </is>
-      </c>
+      <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
+          <t>El procedimiento licitatorio regido por el presente pliego tiene por objeto la Licitación Pública N° 03/2026 para la venta de los siguientes bienes municipales: a) MINI RETRO DE TIRO: Marca RICHIGER, Serie A, N° 101. Modelo N° 186. Motor N° 991023899, C. V 7, 50, Modelo 7, 50 DB, RPM 1.500 b) COLECTIVO: Mercedes Benz, dominio UKZ353, modelo 1977 según lo que s e detalla en el Pliego de Bases y Condiciones que forma parte de la presente como Anexo I</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ) - SI ES DECRETADO INHABIL, AL DIA SIGUIENTE HABIL, A LA MISMA HORA Y LUGA</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>La apertura de sobres se realizará el día 14 de septiembre del 2026 a las 10:00 horas, en la sede municipal</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>El pliego será gratuito. El mismo se encontrará para su consulta y ent</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>id-9e58cc9ec0b69356</t>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>id-ddc4dfb118d357f7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -984,67 +1020,72 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>27/2026</t>
+          <t>76/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
+          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>16 de septiembre de 2026 - Hora: 10:00</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
+          <t>14-09-2026 08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="6" t="inlineStr">
         <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Boletín Oficial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>id-608017f47f903d65</t>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Municipalidad de Paraná</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>id-ccdfae2a7ede4696</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1052,14 +1093,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SEGUÍ</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1069,50 +1110,59 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>08-2026</t>
+          <t>014/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”. Apertura de Sobres 17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y entrega en Área de Suministro del Municipio, y también se podrá descargar en el Sitio Oficial Digital Municipal https://www.segui.gob.ar . Edgardo Muller, Presidente Municipal. ID:52321 - F.C. 04-00075716 3 v./03/09/2026</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y </t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
+          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>id-90c3d1f38f49418a</t>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>id-9e58cc9ec0b69356</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1120,14 +1170,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1137,54 +1187,51 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>015/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
+          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ) - SI ES DECRETADO INHABIL, AL DIA SIGUIENTE HABIL, A LA MISMA HORA Y LUGA</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Boletín Oficial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>id-74dfdad7e5f9d048</t>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Min. Planeamiento (provincia)</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>id-952aef4c115d8f12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1199,7 +1246,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1207,45 +1254,50 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>27/2026</t>
+        </is>
+      </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>16 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>Sin Cargo</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr"/>
       <c r="L11" s="6" t="inlineStr">
         <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>id-bc610b64999d147d</t>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>id-608017f47f903d65</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1319,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ — CONDARCO”</t>
+          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1277,54 +1329,59 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>06/26</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>id-9dbdaa6090d92bd4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1332,14 +1389,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NOGOYA — COMUNA DISTRITO SAUCE -- NOGOYA</t>
+          <t>MUNICIPALIDAD DE SEGUÍ</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1349,54 +1406,55 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>08-2026</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Convocar para la adquisi ción de un Tractor agrícola 0 km, con las siguientes características técnicas: potencia de motor de 130 a 150 HP; doble Tracción, 6 (seis) cilindros; y demás especificación que se encuentran en el pliego de Especificaciones Técnicas</t>
+          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”. Apertura de Sobres 17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y entrega en Área de Suministro del Municipio, y también se podrá descargar en el Sitio Oficial Digital Municipal https://www.segui.gob.ar . Edgardo Muller, Presidente Municipal. ID:52321 - F.C. 04-00075716 3 v./03/09/2026</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>DE PROPUESTAS: Día Viernes 11 de Septiembre de 2026- a las 10:00 horas en la Sede Comunal de Comuna Distrito Sauce</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sin costo. Solicitar en la Sede Comunal de Distrito Sauce Nogoya o al </t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr"/>
       <c r="L13" s="6" t="inlineStr">
         <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>id-328f5a2f67c14702</t>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>id-90c3d1f38f49418a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1404,14 +1462,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1421,54 +1479,59 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>06/26</t>
+          <t>015/2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
-        </is>
-      </c>
-      <c r="K14" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>id-9dbdaa6090d92bd4</t>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>id-74dfdad7e5f9d048</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1493,39 +1556,44 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
+          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
         <is>
           <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>id-952aef4c115d8f12</t>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>id-885d4847519dfd48</t>
         </is>
       </c>
     </row>
@@ -1540,14 +1608,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1555,48 +1623,57 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>10/2026</t>
-        </is>
-      </c>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr"/>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Min. Planeamiento (provincia)</t>
-        </is>
-      </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Sin Cargo</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Boletín Oficial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1611,7 +1688,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — TERMINACION ESCUELA Nº 54</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1621,61 +1698,74 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez realizado el depósito/transferenci</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Min. Planeamiento (provincia)</t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>id-885d4847519dfd48</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN N</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Habilitación: Pesos Ochenta Mil con 0/100 - $ 80.000, 00 - Habilitació</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Boletín Oficial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE ORO VERDE</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — Y PUESTA EN VALOR – ESCUE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1683,67 +1773,76 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>09/2026</t>
+        </is>
+      </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>El procedimiento licitatorio regido por el presente pliego tiene por objeto la Licitación Pública N° 03/2026 para la venta de los siguientes bienes municipales: a) MINI RETRO DE TIRO: Marca RICHIGER, Serie A, N° 101. Modelo N° 186. Motor N° 991023899, C. V 7, 50, Modelo 7, 50 DB, RPM 1.500 b) COLECTIVO: Mercedes Benz, dominio UKZ353, modelo 1977 según lo que s e detalla en el Pliego de Bases y Condiciones que forma parte de la presente como Anexo I</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>La apertura de sobres se realizará el día 14 de septiembre del 2026 a las 10:00 horas, en la sede municipal</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>El pliego será gratuito. El mismo se encontrará para su consulta y ent</t>
-        </is>
-      </c>
-      <c r="K18" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Habilitación: Pesos Ciento Veinte Mil con 0/100 - $ 120.000, 00 - Habi</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>id-ddc4dfb118d357f7</t>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ — CONDARCO”</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1753,61 +1852,74 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>IAPV — Viviendas</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Boletín Oficial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1817,46 +1929,51 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>IAPV — Viviendas</t>
-        </is>
-      </c>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr"/>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Min. Planeamiento (provincia)</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1864,14 +1981,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1881,46 +1998,55 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
-        </is>
-      </c>
+          <t>L LAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>IAPV — Viviendas</t>
-        </is>
-      </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>Ver boletín</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Boletín Oficial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1928,14 +2054,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1945,46 +2071,55 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
-        </is>
-      </c>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr"/>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr"/>
-      <c r="K22" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>IAPV — Viviendas</t>
-        </is>
-      </c>
-      <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>Ver boletín</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>s in cargo Consultas: comprascomuna6to@hotmail.com Celular: 3444- 4493</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Boletín Oficial de Entre Ríos</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2007,44 +2142,49 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>03/26</t>
+        </is>
+      </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
-        </is>
-      </c>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr"/>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
+          <t>Publicada 21/08/2026 — ver pliego</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr"/>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
         <is>
           <t>IAPV — Viviendas</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>id-ebeeb6a87e688d85</t>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2069,46 +2209,47 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
-        </is>
-      </c>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr"/>
-      <c r="K24" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
+          <t>Publicada 09/06/2026 — ver pliego</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr"/>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
         <is>
           <t>IAPV — Viviendas</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
-        <is>
-          <t>id-22811eab8859abaf</t>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2133,46 +2274,47 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
-        </is>
-      </c>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
+          <t>Publicada 05/06/2026 — ver pliego</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr"/>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
         <is>
           <t>IAPV — Viviendas</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>id-c019bf4a08989c09</t>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2197,46 +2339,47 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
-        </is>
-      </c>
+          <t>NOGOYA 19 VIVIENDAS</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
+          <t>Publicada 11/12/2025 — ver pliego</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr"/>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
         <is>
           <t>IAPV — Viviendas</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
-        <is>
-          <t>id-7c1bf02160a66f67</t>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2261,46 +2404,47 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
-        </is>
-      </c>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
+          <t>Publicada 18/11/2025 — ver pliego</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
         <is>
           <t>IAPV — Viviendas</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>id-2b877612500f72b1</t>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2323,41 +2467,38 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>04/2025</t>
-        </is>
-      </c>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
-        </is>
-      </c>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr"/>
-      <c r="K28" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
+          <t>Publicada 11/11/2025 — ver pliego</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr"/>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
         <is>
           <t>IAPV — Viviendas</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
-        <is>
-          <t>id-34c85bcdb9b1123f</t>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
@@ -2372,14 +2513,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2389,54 +2530,47 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>L LAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Ver boletín</t>
-        </is>
-      </c>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
-      <c r="K29" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr"/>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Boletín Oficial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="N29" s="4" t="inlineStr">
-        <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>IAPV — Viviendas</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2444,14 +2578,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2461,54 +2595,47 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Ver boletín</t>
-        </is>
-      </c>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>s in cargo Consultas: comprascomuna6to@hotmail.com Celular: 3444- 4493</t>
-        </is>
-      </c>
-      <c r="K30" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr"/>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Boletín Oficial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="N30" s="4" t="inlineStr">
-        <is>
-          <t>id-511256e6329e386a</t>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>IAPV — Viviendas</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2523,56 +2650,57 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
-        </is>
-      </c>
-      <c r="N31" s="4" t="inlineStr">
-        <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>IAPV — Viviendas</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2580,14 +2708,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2597,46 +2725,47 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>499/26</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
+          <t>Concurso de Precio N° 02/2025</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Túnel Subfluvial</t>
-        </is>
-      </c>
-      <c r="N32" s="4" t="inlineStr">
-        <is>
-          <t>id-f53eab44dba8d43f</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr"/>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>IAPV — Viviendas</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2644,63 +2773,64 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>235/26</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Licitación Privada N° 235/26: reparación de cenefas en losas pórticos</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Túnel Subfluvial</t>
-        </is>
-      </c>
-      <c r="N33" s="4" t="inlineStr">
-        <is>
-          <t>id-22f9c51cdaebefb7</t>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Vialidad Entre Ríos (DPV)</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2708,9 +2838,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2725,46 +2855,47 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>498/26</t>
+          <t>499/26</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA N° 498/26: reparación de un tramo del cerramiento perimetral del Túnel Subfluvial</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
+          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr"/>
-      <c r="K34" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr"/>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
         <is>
           <t>Túnel Subfluvial</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
-        <is>
-          <t>id-46d81e3efd2ae483</t>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>id-f53eab44dba8d43f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2779,29 +2910,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — Y PUESTA EN VALOR – ESCUE</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>235/26</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN </t>
-        </is>
-      </c>
+          <t>Licitación Privada N° 235/26: reparación de cenefas en losas pórticos</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
           <t>Ver pliego</t>
@@ -2809,34 +2936,31 @@
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>Habilitación: Pesos Ciento Veinte Mil con 0/100 - $ 120.000, 00 - Habi</t>
-        </is>
-      </c>
-      <c r="K35" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr"/>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Boletín Oficial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="N35" s="4" t="inlineStr">
-        <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Túnel Subfluvial</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>id-22f9c51cdaebefb7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2851,7 +2975,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — TERMINACION ESCUELA Nº 54</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2861,19 +2985,15 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>498/26</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez realizado el depósito/transferenci</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN N</t>
-        </is>
-      </c>
+          <t>LICITACIÓN PÚBLICA N° 498/26: reparación de un tramo del cerramiento perimetral del Túnel Subfluvial</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
           <t>Ver pliego</t>
@@ -2881,85 +3001,82 @@
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>Habilitación: Pesos Ochenta Mil con 0/100 - $ 80.000, 00 - Habilitació</t>
-        </is>
-      </c>
-      <c r="K36" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr"/>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Boletín Oficial de Entre Ríos</t>
-        </is>
-      </c>
-      <c r="N36" s="4" t="inlineStr">
-        <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Túnel Subfluvial</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>id-46d81e3efd2ae483</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N36"/>
+  <autoFilter ref="A1:O36"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -62,12 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -651,39 +651,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CONCORDIA — MUNICIPALIDAD DE PUERTO YERUA</t>
+          <t>MUNICIPALIDAD DE CHAJARI — APERTURA: 08 DE SEPTIEMBRE DE 2026 - HORA: 10:00 (DIEZ) - SI ES</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitacion Publica</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>1/2026</t>
+          <t>013/2026</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de una motoniveladora 0 Km</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – hierro y otros – que serán destinados a la construcción de viviendas que se llevarán a cabo en el marco del Plan Construir Futuro 7</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>08 DE SEPTIEMBRE DE 2026 - HORA: 10:00 (DIEZ)</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -691,7 +691,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>$ 100.000,00.- (PESOS CIEN MIL CON 00/100) PRESUPUESTO OFICIAL ESTIMAD</t>
+        </is>
+      </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -709,7 +713,7 @@
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>id-61b6e4f9568150b0</t>
+          <t>id-2ac90305e5165aad</t>
         </is>
       </c>
     </row>
@@ -724,14 +728,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NOGOYA — COMUNA DISTRITO SAUCE -- NOGOYA</t>
+          <t>FEDERACION — COMUNA DE SAN PEDRO -- DEPARTAMENTO DE FEDERACIÓN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -741,22 +745,22 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Convocar para la adquisi ción de un Tractor agrícola 0 km, con las siguientes características técnicas: potencia de motor de 130 a 150 HP; doble Tracción, 6 (seis) cilindros; y demás especificación que se encuentran en el pliego de Especificaciones Técnicas</t>
+          <t>“PROVISION RIPIO SELECCIONADO EN ORIGEN Y ENTREGADO SOBRE TRANSPORTE”</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Viernes 11 de Septiembre de 2026- a las 10:00 horas en la Sede Comunal de Comuna Distrito Sauce</t>
+          <t>09 de Septiembre de 2026 - 10:00 hs</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -766,7 +770,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sin costo. Solicitar en la Sede Comunal de Distrito Sauce Nogoya o al </t>
+          <t>Sin costo</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -786,7 +790,7 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>id-328f5a2f67c14702</t>
+          <t>id-719cc55444d8579b</t>
         </is>
       </c>
     </row>
@@ -808,32 +812,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>CONCORDIA — MUNICIPALIDAD DE PUERTO YERUA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>77/2026</t>
+          <t>1/2026</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>ADQUISICION DE CAMIONETAS</t>
+          <t>Adquisición de una motoniveladora 0 Km</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>11-09-2026 08:00</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -854,12 +858,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>id-dff70529581309e6</t>
+          <t>id-61b6e4f9568150b0</t>
         </is>
       </c>
     </row>
@@ -874,14 +878,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>Áridos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
+          <t>ENTE INTERPROVINCIAL TUNEL SUBFLUVIAL RAUL URANGA -- CARLOS S. BEGNIS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -889,24 +893,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>06/2026</t>
-        </is>
-      </c>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>14 de septiembre de 2026 - Hora: 10:00</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -914,7 +914,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>GRATUITO FECHA DE APERTURA: 10/09/2026</t>
+        </is>
+      </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -932,7 +936,7 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-85e6cfd11c8a8889</t>
+          <t>id-439ddd7aaa7f7b3e</t>
         </is>
       </c>
     </row>
@@ -954,7 +958,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE ORO VERDE</t>
+          <t>NOGOYA — COMUNA DISTRITO SAUCE -- NOGOYA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -962,20 +966,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1/26</t>
+        </is>
+      </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>El procedimiento licitatorio regido por el presente pliego tiene por objeto la Licitación Pública N° 03/2026 para la venta de los siguientes bienes municipales: a) MINI RETRO DE TIRO: Marca RICHIGER, Serie A, N° 101. Modelo N° 186. Motor N° 991023899, C. V 7, 50, Modelo 7, 50 DB, RPM 1.500 b) COLECTIVO: Mercedes Benz, dominio UKZ353, modelo 1977 según lo que s e detalla en el Pliego de Bases y Condiciones que forma parte de la presente como Anexo I</t>
+          <t>Convocar para la adquisi ción de un Tractor agrícola 0 km, con las siguientes características técnicas: potencia de motor de 130 a 150 HP; doble Tracción, 6 (seis) cilindros; y demás especificación que se encuentran en el pliego de Especificaciones Técnicas</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>La apertura de sobres se realizará el día 14 de septiembre del 2026 a las 10:00 horas, en la sede municipal</t>
+          <t>Viernes 11 de Septiembre de 2026- a las 10:00 horas en la Sede Comunal de Comuna Distrito Sauce</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -985,7 +993,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>El pliego será gratuito. El mismo se encontrará para su consulta y ent</t>
+          <t xml:space="preserve">sin costo. Solicitar en la Sede Comunal de Distrito Sauce Nogoya o al </t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -1005,7 +1013,7 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-ddc4dfb118d357f7</t>
+          <t>id-328f5a2f67c14702</t>
         </is>
       </c>
     </row>
@@ -1037,22 +1045,22 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>76/2026</t>
+          <t>77/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
+          <t>ADQUISICION DE CAMIONETAS</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>14-09-2026 08:00</t>
+          <t>11-09-2026 08:00</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1078,7 +1086,7 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-ccdfae2a7ede4696</t>
+          <t>id-dff70529581309e6</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1103,12 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
+          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1110,22 +1118,22 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>014/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
+          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>14 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1133,11 +1141,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
-        </is>
-      </c>
+      <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1155,7 +1159,7 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-9e58cc9ec0b69356</t>
+          <t>id-85e6cfd11c8a8889</t>
         </is>
       </c>
     </row>
@@ -1170,14 +1174,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>MUNICIPIO DE ORO VERDE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1185,24 +1189,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>08/2026</t>
-        </is>
-      </c>
+      <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
+          <t>El procedimiento licitatorio regido por el presente pliego tiene por objeto la Licitación Pública N° 03/2026 para la venta de los siguientes bienes municipales: a) MINI RETRO DE TIRO: Marca RICHIGER, Serie A, N° 101. Modelo N° 186. Motor N° 991023899, C. V 7, 50, Modelo 7, 50 DB, RPM 1.500 b) COLECTIVO: Mercedes Benz, dominio UKZ353, modelo 1977 según lo que s e detalla en el Pliego de Bases y Condiciones que forma parte de la presente como Anexo I</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
+          <t>La apertura de sobres se realizará el día 14 de septiembre del 2026 a las 10:00 horas, en la sede municipal</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1210,21 +1210,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>El pliego será gratuito. El mismo se encontrará para su consulta y ent</t>
+        </is>
+      </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-952aef4c115d8f12</t>
+          <t>id-ddc4dfb118d357f7</t>
         </is>
       </c>
     </row>
@@ -1239,39 +1247,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>27/2026</t>
+          <t>76/2026</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
+          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>16 de septiembre de 2026 - Hora: 10:00</t>
+          <t>14-09-2026 08:00</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1292,12 +1300,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-608017f47f903d65</t>
+          <t>id-ccdfae2a7ede4696</t>
         </is>
       </c>
     </row>
@@ -1312,14 +1320,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1329,22 +1337,22 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>06/26</t>
+          <t>014/2026</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en calle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
+          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1354,7 +1362,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
+          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -1374,7 +1382,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-9dbdaa6090d92bd4</t>
+          <t>id-9e58cc9ec0b69356</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1404,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SEGUÍ</t>
+          <t xml:space="preserve">ELECTRICA, CUBIERTA DE TECHO Y REFACCION DE BAÑOS ESCUELA Nº 1 “JOSE MARIA TEXIER” -SAN — </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1406,30 +1414,34 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>08-2026</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”. Apertura de Sobres 17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y entrega en Área de Suministro del Municipio, y también se podrá descargar en el Sitio Oficial Digital Municipal https://www.segui.gob.ar . Edgardo Muller, Presidente Municipal. ID:52321 - F.C. 04-00075716 3 v./03/09/2026</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “NUEVA INSTALACION ELECTRICA, CUBIERTA DE TECHO Y REFACCION DE BAÑOS ESCUELA Nº 1 “JOSE MARIA TEXIER” -SAN SALVADOR-DEPARTAMENTO SAN SALVADOR.”</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y</t>
+          <t>DE LAS OFERTAS: el día 15 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1447,7 +1459,7 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-90c3d1f38f49418a</t>
+          <t>id-fb80c8ade7a8651d</t>
         </is>
       </c>
     </row>
@@ -1462,14 +1474,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1479,22 +1491,22 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>015/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
+          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1502,29 +1514,21 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
-        </is>
-      </c>
+      <c r="K14" s="4" t="inlineStr"/>
       <c r="L14" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M14" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-74dfdad7e5f9d048</t>
+          <t>id-952aef4c115d8f12</t>
         </is>
       </c>
     </row>
@@ -1539,14 +1543,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1556,22 +1560,22 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>27/2026</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>16 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1585,15 +1589,19 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-885d4847519dfd48</t>
+          <t>id-608017f47f903d65</t>
         </is>
       </c>
     </row>
@@ -1608,14 +1616,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1623,20 +1631,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>06/26</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1646,7 +1658,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Sin Cargo</t>
+          <t>PESOS CINCUEN TA MIL ($ 50.000)</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -1666,7 +1678,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-9dbdaa6090d92bd4</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1700,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — TERMINACION ESCUELA Nº 54</t>
+          <t>MUNICIPALIDAD DE SEGUÍ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1698,22 +1710,22 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>08-2026</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez realizado el depósito/transferenci</t>
+          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Usos Múltiples – Gimnasio Municipal”. Apertura de Sobres 17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y entrega en Área de Suministro del Municipio, y también se podrá descargar en el Sitio Oficial Digital Municipal https://www.segui.gob.ar . Edgardo Muller, Presidente Municipal. ID:52321 - F.C. 04-00075716 3 v./03/09/2026</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN N</t>
+          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1721,11 +1733,7 @@
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Habilitación: Pesos Ochenta Mil con 0/100 - $ 80.000, 00 - Habilitació</t>
-        </is>
-      </c>
+      <c r="K17" s="4" t="inlineStr"/>
       <c r="L17" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1743,7 +1751,7 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-90c3d1f38f49418a</t>
         </is>
       </c>
     </row>
@@ -1758,14 +1766,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — Y PUESTA EN VALOR – ESCUE</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1775,32 +1783,32 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>015/2026</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN</t>
+          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Habilitación: Pesos Ciento Veinte Mil con 0/100 - $ 120.000, 00 - Habi</t>
+          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -1820,7 +1828,7 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-74dfdad7e5f9d048</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1850,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ — CONDARCO”</t>
+          <t>RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION — ELECTRICA-E</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1852,22 +1860,22 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>09/26</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1897,7 +1905,7 @@
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-6a4a84712fd41a03</t>
         </is>
       </c>
     </row>
@@ -1929,22 +1937,22 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1966,7 +1974,7 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-885d4847519dfd48</t>
         </is>
       </c>
     </row>
@@ -1976,19 +1984,19 @@
           <t>08/09/2026</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1996,20 +2004,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>001-2026</t>
-        </is>
-      </c>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>L LAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr"/>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2019,7 +2027,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>Sin Cargo</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -2039,7 +2047,7 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -2049,19 +2057,19 @@
           <t>08/09/2026</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — TERMINACION ESCUELA Nº 54</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2071,28 +2079,32 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr"/>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez realizado el depósito/transferenci</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN N</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>s in cargo Consultas: comprascomuna6to@hotmail.com Celular: 3444- 4493</t>
+          <t>Habilitación: Pesos Ochenta Mil con 0/100 - $ 80.000, 00 - Habilitació</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -2112,7 +2124,7 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
@@ -2122,19 +2134,19 @@
           <t>08/09/2026</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — Y PUESTA EN VALOR – ESCUE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2144,40 +2156,52 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr"/>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr"/>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Habilitación: Pesos Ciento Veinte Mil con 0/100 - $ 120.000, 00 - Habi</t>
+        </is>
+      </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
@@ -2187,19 +2211,19 @@
           <t>08/09/2026</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ — CONDARCO”</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2209,18 +2233,22 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr"/>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2228,21 +2256,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2252,19 +2288,19 @@
           <t>08/09/2026</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2274,18 +2310,22 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr"/>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2302,12 +2342,12 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
@@ -2322,14 +2362,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2339,18 +2379,18 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>L LAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2358,21 +2398,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2387,14 +2435,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2404,18 +2452,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2423,21 +2471,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>s in cargo Consultas: comprascomuna6to@hotmail.com Celular: 3444- 4493</t>
+        </is>
+      </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2508,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2467,16 +2523,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>03/26</t>
+        </is>
+      </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2498,7 +2558,7 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2573,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2530,18 +2590,18 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>04/2025</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2563,7 +2623,7 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2638,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2595,18 +2655,18 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2628,7 +2688,7 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2703,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2660,18 +2720,18 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2693,7 +2753,7 @@
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2768,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2725,18 +2785,18 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2758,7 +2818,7 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
@@ -2773,35 +2833,31 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Concurso</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>01/26</t>
-        </is>
-      </c>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2818,12 +2874,12 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
@@ -2840,12 +2896,12 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Áridos</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2855,18 +2911,18 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>499/26</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2883,12 +2939,12 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-f53eab44dba8d43f</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
@@ -2903,35 +2959,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>235/26</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Licitación Privada N° 235/26: reparación de cenefas en losas pórticos</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2948,12 +3004,12 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-22f9c51cdaebefb7</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
@@ -2968,14 +3024,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2985,18 +3041,18 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>498/26</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA N° 498/26: reparación de un tramo del cerramiento perimetral del Túnel Subfluvial</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3013,17 +3069,342 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
+          <t>IAPV — Viviendas</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>id-07ddb93a12c5a870</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>IAPV (Vivienda)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Concurso de Precio N° 02/2025</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>Publicada 19/06/2025 — ver pliego</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>IAPV — Viviendas</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>id-7c1bf02160a66f67</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Vialidad Entre Ríos (DPV)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Concurso</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>01/26</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr"/>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Vialidad Entre Ríos (DPV)</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>id-9a16884dd5a64a49</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Áridos</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>Túnel Subfluvial</t>
         </is>
       </c>
-      <c r="O36" s="4" t="inlineStr">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>499/26</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr"/>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Túnel Subfluvial</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>id-f53eab44dba8d43f</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Túnel Subfluvial</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Licitación Privada</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>235/26</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Licitación Privada N° 235/26: reparación de cenefas en losas pórticos</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr"/>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Túnel Subfluvial</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>id-22f9c51cdaebefb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Túnel Subfluvial</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>498/26</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>LICITACIÓN PÚBLICA N° 498/26: reparación de un tramo del cerramiento perimetral del Túnel Subfluvial</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Túnel Subfluvial</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
         <is>
           <t>id-46d81e3efd2ae483</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O36"/>
+  <autoFilter ref="A1:O41"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3042,42 +3423,52 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -1327,7 +1327,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en calle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>PESOS CINCUEN TA MIL ($ 50.000)</t>
+          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Usos Múltiples – Gimnasio Municipal”. Apertura de Sobres 17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y entrega en Área de Suministro del Municipio, y también se podrá descargar en el Sitio Oficial Digital Municipal https://www.segui.gob.ar . Edgardo Muller, Presidente Municipal. ID:52321 - F.C. 04-00075716 3 v./03/09/2026</t>
+          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”. Apertura de Sobres 17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y entrega en Área de Suministro del Municipio, y también se podrá descargar en el Sitio Oficial Digital Municipal https://www.segui.gob.ar . Edgardo Muller, Presidente Municipal. ID:52321 - F.C. 04-00075716 3 v./03/09/2026</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -658,7 +658,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CHAJARI — APERTURA: 08 DE SEPTIEMBRE DE 2026 - HORA: 10:00 (DIEZ) - SI ES</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELECTRICA, CUBIERTA DE TECHO Y REFACCION DE BAÑOS ESCUELA Nº 1 “JOSE MARIA TEXIER” -SAN — </t>
+          <t>MINISTERIO DE PLANEAMIENTO E INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION — ELECTRICA-E</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — TERMINACION ESCUELA Nº 54</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE — Y PUESTA EN VALOR – ESCUE</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ — CONDARCO”</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -62,12 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -566,7 +566,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -653,37 +653,37 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
+          <t>FEDERACION — COMUNA DE SAN PEDRO -- DEPARTAMENTO DE FEDERACIÓN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Licitacion Publica</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>013/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – hierro y otros – que serán destinados a la construcción de viviendas que se llevarán a cabo en el marco del Plan Construir Futuro 7</t>
+          <t>“PROVISION RIPIO SELECCIONADO EN ORIGEN Y ENTREGADO SOBRE TRANSPORTE”</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>08 DE SEPTIEMBRE DE 2026 - HORA: 10:00 (DIEZ)</t>
+          <t>09 de Septiembre de 2026 - 10:00 hs</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>$ 100.000,00.- (PESOS CIEN MIL CON 00/100) PRESUPUESTO OFICIAL ESTIMAD</t>
+          <t>Sin costo</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -713,14 +713,14 @@
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>id-2ac90305e5165aad</t>
+          <t>id-719cc55444d8579b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -728,14 +728,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FEDERACION — COMUNA DE SAN PEDRO -- DEPARTAMENTO DE FEDERACIÓN</t>
+          <t>CONCORDIA — MUNICIPALIDAD DE PUERTO YERUA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -745,22 +745,22 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>1/2026</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION RIPIO SELECCIONADO EN ORIGEN Y ENTREGADO SOBRE TRANSPORTE”</t>
+          <t>Adquisición de una motoniveladora 0 Km</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>09 de Septiembre de 2026 - 10:00 hs</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -768,11 +768,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>Sin costo</t>
-        </is>
-      </c>
+      <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -790,14 +786,14 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>id-719cc55444d8579b</t>
+          <t>id-61b6e4f9568150b0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -805,14 +801,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CONCORDIA — MUNICIPALIDAD DE PUERTO YERUA</t>
+          <t>ENTE INTERPROVINCIAL TUNEL SUBFLUVIAL RAUL URANGA -- CARLOS S. BEGNIS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -820,14 +816,10 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1/2026</t>
-        </is>
-      </c>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de una motoniveladora 0 Km</t>
+          <t>EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -845,7 +837,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>GRATUITO FECHA DE APERTURA: 10/09/2026</t>
+        </is>
+      </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -863,14 +859,14 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>id-61b6e4f9568150b0</t>
+          <t>id-439ddd7aaa7f7b3e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -878,14 +874,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ENTE INTERPROVINCIAL TUNEL SUBFLUVIAL RAUL URANGA -- CARLOS S. BEGNIS</t>
+          <t>NOGOYA — COMUNA DISTRITO SAUCE -- NOGOYA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -893,20 +889,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1/26</t>
+        </is>
+      </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
+          <t>Convocar para la adquisi ción de un Tractor agrícola 0 km, con las siguientes características técnicas: potencia de motor de 130 a 150 HP; doble Tracción, 6 (seis) cilindros; y demás especificación que se encuentran en el pliego de Especificaciones Técnicas</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>Viernes 11 de Septiembre de 2026- a las 10:00 horas en la Sede Comunal de Comuna Distrito Sauce</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>GRATUITO FECHA DE APERTURA: 10/09/2026</t>
+          <t xml:space="preserve">sin costo. Solicitar en la Sede Comunal de Distrito Sauce Nogoya o al </t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -936,14 +936,14 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-439ddd7aaa7f7b3e</t>
+          <t>id-328f5a2f67c14702</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -958,22 +958,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NOGOYA — COMUNA DISTRITO SAUCE -- NOGOYA</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>77/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Convocar para la adquisi ción de un Tractor agrícola 0 km, con las siguientes características técnicas: potencia de motor de 130 a 150 HP; doble Tracción, 6 (seis) cilindros; y demás especificación que se encuentran en el pliego de Especificaciones Técnicas</t>
+          <t>ADQUISICION DE CAMIONETAS</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Viernes 11 de Septiembre de 2026- a las 10:00 horas en la Sede Comunal de Comuna Distrito Sauce</t>
+          <t>11-09-2026 08:00</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -991,11 +991,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sin costo. Solicitar en la Sede Comunal de Distrito Sauce Nogoya o al </t>
-        </is>
-      </c>
+      <c r="K7" s="4" t="inlineStr"/>
       <c r="L7" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1008,19 +1004,19 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-328f5a2f67c14702</t>
+          <t>id-dff70529581309e6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1028,39 +1024,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>77/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>ADQUISICION DE CAMIONETAS</t>
+          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>11-09-2026 08:00</t>
+          <t>14 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1081,19 +1077,19 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-dff70529581309e6</t>
+          <t>id-85e6cfd11c8a8889</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1101,14 +1097,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
+          <t>MUNICIPIO DE ORO VERDE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1116,14 +1112,10 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>06/2026</t>
-        </is>
-      </c>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>El procedimiento licitatorio regido por el presente pliego tiene por objeto la Licitación Pública N° 03/2026 para la venta de los siguientes bienes municipales: a) MINI RETRO DE TIRO: Marca RICHIGER, Serie A, N° 101. Modelo N° 186. Motor N° 991023899, C. V 7, 50, Modelo 7, 50 DB, RPM 1.500 b) COLECTIVO: Mercedes Benz, dominio UKZ353, modelo 1977 según lo que s e detalla en el Pliego de Bases y Condiciones que forma parte de la presente como Anexo I</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1133,7 +1125,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>14 de septiembre de 2026 - Hora: 10:00</t>
+          <t>La apertura de sobres se realizará el día 14 de septiembre del 2026 a las 10:00 horas, en la sede municipal</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1141,7 +1133,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>El pliego será gratuito. El mismo se encontrará para su consulta y ent</t>
+        </is>
+      </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1159,14 +1155,14 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-85e6cfd11c8a8889</t>
+          <t>id-ddc4dfb118d357f7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1181,18 +1177,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE ORO VERDE</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr"/>
+          <t>LICITACIÓN PÚBLICA</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>76/2026</t>
+        </is>
+      </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>El procedimiento licitatorio regido por el presente pliego tiene por objeto la Licitación Pública N° 03/2026 para la venta de los siguientes bienes municipales: a) MINI RETRO DE TIRO: Marca RICHIGER, Serie A, N° 101. Modelo N° 186. Motor N° 991023899, C. V 7, 50, Modelo 7, 50 DB, RPM 1.500 b) COLECTIVO: Mercedes Benz, dominio UKZ353, modelo 1977 según lo que s e detalla en el Pliego de Bases y Condiciones que forma parte de la presente como Anexo I</t>
+          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>La apertura de sobres se realizará el día 14 de septiembre del 2026 a las 10:00 horas, en la sede municipal</t>
+          <t>14-09-2026 08:00</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1210,11 +1210,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>El pliego será gratuito. El mismo se encontrará para su consulta y ent</t>
-        </is>
-      </c>
+      <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1227,19 +1223,19 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-ddc4dfb118d357f7</t>
+          <t>id-ccdfae2a7ede4696</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1247,39 +1243,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>76/2026</t>
+          <t>014/2026</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>14-09-2026 08:00</t>
+          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1287,7 +1283,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
+        </is>
+      </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1300,19 +1300,19 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-ccdfae2a7ede4696</t>
+          <t>id-9e58cc9ec0b69356</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1320,14 +1320,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
+          <t>MINISTERIO DE PLANEAMIENTO E INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>014/2026</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “NUEVA INSTALACION ELECTRICA, CUBIERTA DE TECHO Y REFACCION DE BAÑOS ESCUELA Nº 1 “JOSE MARIA TEXIER” -SAN SALVADOR-DEPARTAMENTO SAN SALVADOR.”</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>DE LAS OFERTAS: el día 15 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -1382,14 +1382,14 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-9e58cc9ec0b69356</t>
+          <t>id-fb80c8ade7a8651d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO E INFRAESTRUCTURA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “NUEVA INSTALACION ELECTRICA, CUBIERTA DE TECHO Y REFACCION DE BAÑOS ESCUELA Nº 1 “JOSE MARIA TEXIER” -SAN SALVADOR-DEPARTAMENTO SAN SALVADOR.”</t>
+          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 15 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1437,36 +1437,28 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K13" s="4" t="inlineStr"/>
       <c r="L13" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-fb80c8ade7a8651d</t>
+          <t>id-952aef4c115d8f12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1474,14 +1466,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1491,22 +1483,22 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>27/2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
+          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
+          <t>16 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1520,22 +1512,26 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-952aef4c115d8f12</t>
+          <t>id-608017f47f903d65</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1543,14 +1539,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
+          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1560,22 +1556,22 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>27/2026</t>
+          <t>06/26</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
+          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>16 de septiembre de 2026 - Hora: 10:00</t>
+          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1583,7 +1579,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
+        </is>
+      </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1601,14 +1601,14 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-608017f47f903d65</t>
+          <t>id-9dbdaa6090d92bd4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
+          <t>MUNICIPALIDAD DE SEGUÍ</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1633,12 +1633,12 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>06/26</t>
+          <t>08-2026</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
+          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”. Apertura de Sobres 17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y entrega en Área de Suministro del Municipio, y también se podrá descargar en el Sitio Oficial Digital Municipal https://www.segui.gob.ar . Edgardo Muller, Presidente Municipal. ID:52321 - F.C. 04-00075716 3 v./03/09/2026</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1648,19 +1648,15 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
+          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1678,14 +1674,14 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-9dbdaa6090d92bd4</t>
+          <t>id-90c3d1f38f49418a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1693,14 +1689,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SEGUÍ</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1710,30 +1706,34 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>08-2026</t>
+          <t>015/2026</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”. Apertura de Sobres 17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y entrega en Área de Suministro del Municipio, y también se podrá descargar en el Sitio Oficial Digital Municipal https://www.segui.gob.ar . Edgardo Muller, Presidente Municipal. ID:52321 - F.C. 04-00075716 3 v./03/09/2026</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y</t>
+          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
+        </is>
+      </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1751,14 +1751,14 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-90c3d1f38f49418a</t>
+          <t>id-74dfdad7e5f9d048</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1766,14 +1766,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1783,12 +1783,12 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>015/2026</t>
+          <t>09/26</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -1828,14 +1828,14 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-74dfdad7e5f9d048</t>
+          <t>id-6a4a84712fd41a03</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>09/26</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
+          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1883,36 +1883,28 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K19" s="4" t="inlineStr"/>
       <c r="L19" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M19" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-6a4a84712fd41a03</t>
+          <t>id-885d4847519dfd48</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1920,14 +1912,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1935,24 +1927,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>09/2026</t>
-        </is>
-      </c>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1960,28 +1948,36 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Sin Cargo</t>
+        </is>
+      </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-885d4847519dfd48</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1989,14 +1985,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2004,10 +2000,14 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez realizado el depósito/transferenci</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -2017,17 +2017,17 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN N</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>Sin Cargo</t>
+          <t>Habilitación: Pesos Ochenta Mil con 0/100 - $ 80.000, 00 - Habilitació</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -2047,14 +2047,14 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez realizado el depósito/transferenci</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN N</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>Habilitación: Pesos Ochenta Mil con 0/100 - $ 80.000, 00 - Habilitació</t>
+          <t>Habilitación: Pesos Ciento Veinte Mil con 0/100 - $ 120.000, 00 - Habi</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -2124,14 +2124,14 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2156,32 +2156,32 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>Habilitación: Pesos Ciento Veinte Mil con 0/100 - $ 120.000, 00 - Habi</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
@@ -2201,14 +2201,14 @@
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2256,41 +2256,33 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M24" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -2300,7 +2292,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2310,22 +2302,18 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>L LAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2333,28 +2321,36 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2362,14 +2358,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2379,12 +2375,12 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>L LAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -2400,7 +2396,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>s in cargo Consultas: comprascomuna6to@hotmail.com Celular: 3444- 4493</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
@@ -2420,14 +2416,14 @@
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2435,14 +2431,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2452,18 +2448,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>03/26</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2471,36 +2467,28 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>s in cargo Consultas: comprascomuna6to@hotmail.com Celular: 3444- 4493</t>
-        </is>
-      </c>
+      <c r="K27" s="4" t="inlineStr"/>
       <c r="L27" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M27" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2508,7 +2496,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2525,18 +2513,18 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2558,14 +2546,14 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2573,7 +2561,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2590,18 +2578,18 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2623,14 +2611,14 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2638,7 +2626,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2655,18 +2643,18 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2688,14 +2676,14 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2703,7 +2691,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2720,18 +2708,18 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2753,14 +2741,14 @@
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2768,7 +2756,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2783,20 +2771,16 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>06/2025</t>
-        </is>
-      </c>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2818,14 +2802,14 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2833,7 +2817,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2848,16 +2832,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>04/2025</t>
+        </is>
+      </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2879,14 +2867,14 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2894,7 +2882,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2911,18 +2899,18 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>04/2025</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2944,14 +2932,14 @@
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2959,7 +2947,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2976,18 +2964,18 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3009,14 +2997,14 @@
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3024,7 +3012,7 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -3046,13 +3034,13 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3074,14 +3062,14 @@
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3089,35 +3077,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3134,19 +3122,19 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3156,27 +3144,27 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>499/26</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -3199,19 +3187,19 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-f53eab44dba8d43f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3219,9 +3207,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3231,17 +3219,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>499/26</t>
+          <t>235/26</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
+          <t>Licitación Privada N° 235/26: reparación de cenefas en losas pórticos</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -3269,14 +3257,14 @@
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>id-f53eab44dba8d43f</t>
+          <t>id-22f9c51cdaebefb7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3296,17 +3284,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>235/26</t>
+          <t>498/26</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Licitación Privada N° 235/26: reparación de cenefas en losas pórticos</t>
+          <t>LICITACIÓN PÚBLICA N° 498/26: reparación de un tramo del cerramiento perimetral del Túnel Subfluvial</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -3334,77 +3322,12 @@
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>id-22f9c51cdaebefb7</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>08/09/2026</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Túnel Subfluvial</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>498/26</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>LICITACIÓN PÚBLICA N° 498/26: reparación de un tramo del cerramiento perimetral del Túnel Subfluvial</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr"/>
-      <c r="L41" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Túnel Subfluvial</t>
-        </is>
-      </c>
-      <c r="O41" s="4" t="inlineStr">
-        <is>
           <t>id-46d81e3efd2ae483</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O41"/>
+  <autoFilter ref="A1:O40"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3429,8 +3352,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId28"/>
@@ -3440,8 +3363,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId39"/>
@@ -3449,26 +3372,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, C ondiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1243,14 +1243,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
+          <t>MUNICIPALIDAD DE HERRERA — DPTO. URUGUAY, ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>014/2026</t>
+          <t>01-2026</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
+          <t>Adquisición de vehículo 0 km destinado al traslado de personas tipo van, con capacidad para 11 plazas (1 conductor + 10 pasajeros), motorización a nafta/diesel, según pliego de espec ificaciones técnicas</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>DE LAS OFERTAS: el día 15/09/2026, a las 11:00 hs. en el Edificio Municipal de Herrera, sito en Av. H. Bozzolo, Nº 165,</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-9e58cc9ec0b69356</t>
+          <t>id-28313c7a9524d0ee</t>
         </is>
       </c>
     </row>
@@ -1320,14 +1320,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO E INFRAESTRUCTURA</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>014/2026</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “NUEVA INSTALACION ELECTRICA, CUBIERTA DE TECHO Y REFACCION DE BAÑOS ESCUELA Nº 1 “JOSE MARIA TEXIER” -SAN SALVADOR-DEPARTAMENTO SAN SALVADOR.”</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 15 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-fb80c8ade7a8651d</t>
+          <t>id-9e58cc9ec0b69356</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>MINISTERIO DE PLANEAMIENTO E INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “NUEVA INSTALACION ELECTRICA, CUBIERTA DE TECHO Y REFACCION DE BAÑOS ESCUELA Nº 1 “JOSE MARIA TEXIER” -SAN SALVADOR-DEPARTAMENTO SAN SALVADOR.”</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
+          <t>DE LAS OFERTAS: el día 15 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1437,21 +1437,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-952aef4c115d8f12</t>
+          <t>id-fb80c8ade7a8651d</t>
         </is>
       </c>
     </row>
@@ -1466,14 +1474,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1483,22 +1491,22 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>27/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
+          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>16 de septiembre de 2026 - Hora: 10:00</t>
+          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1512,19 +1520,15 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M14" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-608017f47f903d65</t>
+          <t>id-952aef4c115d8f12</t>
         </is>
       </c>
     </row>
@@ -1539,14 +1543,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1556,22 +1560,22 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>06/26</t>
+          <t>27/2026</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
+          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
+          <t>16 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1579,11 +1583,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
-        </is>
-      </c>
+      <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-9dbdaa6090d92bd4</t>
+          <t>id-608017f47f903d65</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SEGUÍ</t>
+          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1633,12 +1633,12 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>08-2026</t>
+          <t>06/26</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”. Apertura de Sobres 17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y entrega en Área de Suministro del Municipio, y también se podrá descargar en el Sitio Oficial Digital Municipal https://www.segui.gob.ar . Edgardo Muller, Presidente Municipal. ID:52321 - F.C. 04-00075716 3 v./03/09/2026</t>
+          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1648,15 +1648,19 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y</t>
+          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
+        </is>
+      </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1674,7 +1678,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-90c3d1f38f49418a</t>
+          <t>id-9dbdaa6090d92bd4</t>
         </is>
       </c>
     </row>
@@ -1689,14 +1693,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>MUNICIPALIDAD DE SEGUÍ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1706,34 +1710,30 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>015/2026</t>
+          <t>08-2026</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
+          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”. Apertura de Sobres 17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y entrega en Área de Suministro del Municipio, y también se podrá descargar en el Sitio Oficial Digital Municipal https://www.segui.gob.ar . Edgardo Muller, Presidente Municipal. ID:52321 - F.C. 04-00075716 3 v./03/09/2026</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr"/>
       <c r="L17" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-74dfdad7e5f9d048</t>
+          <t>id-90c3d1f38f49418a</t>
         </is>
       </c>
     </row>
@@ -1766,14 +1766,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1783,12 +1783,12 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>09/26</t>
+          <t>015/2026</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-6a4a84712fd41a03</t>
+          <t>id-74dfdad7e5f9d048</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>09/26</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1883,21 +1883,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-885d4847519dfd48</t>
+          <t>id-6a4a84712fd41a03</t>
         </is>
       </c>
     </row>
@@ -1912,14 +1920,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1927,20 +1935,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>09/2026</t>
+        </is>
+      </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1948,29 +1960,21 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>Sin Cargo</t>
-        </is>
-      </c>
+      <c r="K20" s="4" t="inlineStr"/>
       <c r="L20" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M20" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-885d4847519dfd48</t>
         </is>
       </c>
     </row>
@@ -1985,14 +1989,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2000,14 +2004,10 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>10/2026</t>
-        </is>
-      </c>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez realizado el depósito/transferenci</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -2017,17 +2017,17 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN N</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>Habilitación: Pesos Ochenta Mil con 0/100 - $ 80.000, 00 - Habilitació</t>
+          <t>Sin Cargo</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez realizado el depósito/transferenci</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN N</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>Habilitación: Pesos Ciento Veinte Mil con 0/100 - $ 120.000, 00 - Habi</t>
+          <t>Habilitación: Pesos Ochenta Mil con 0/100 - $ 80.000, 00 - Habilitació</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2156,32 +2156,32 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>Habilitación: Pesos Ciento Veinte Mil con 0/100 - $ 120.000, 00 - Habi</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2256,21 +2256,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2280,9 +2288,9 @@
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -2292,7 +2300,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2302,18 +2310,22 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>L LAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr"/>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2321,29 +2333,21 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K25" s="4" t="inlineStr"/>
       <c r="L25" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M25" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
@@ -2358,14 +2362,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2375,18 +2379,18 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2396,7 +2400,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>s in cargo Consultas: comprascomuna6to@hotmail.com Celular: 3444- 4493</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
@@ -2416,7 +2420,7 @@
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2431,14 +2435,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2448,18 +2452,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2467,21 +2471,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>s in cargo Consultas: comprascomuna6to@hotmail.com Celular: 3444- 4493</t>
+        </is>
+      </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2513,18 +2525,18 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>03/26</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2546,7 +2558,7 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
@@ -2578,18 +2590,18 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2611,7 +2623,7 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
@@ -2643,18 +2655,18 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2676,7 +2688,7 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
@@ -2708,18 +2720,18 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2741,7 +2753,7 @@
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
@@ -2771,16 +2783,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>06/2025</t>
+        </is>
+      </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2802,7 +2818,7 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
@@ -2832,20 +2848,16 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>04/2025</t>
-        </is>
-      </c>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2867,7 +2879,7 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
@@ -2899,18 +2911,18 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2932,7 +2944,7 @@
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
@@ -2964,18 +2976,18 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2997,7 +3009,7 @@
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
@@ -3034,13 +3046,13 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3062,7 +3074,7 @@
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -3084,28 +3096,28 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3122,12 +3134,12 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -3142,29 +3154,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>499/26</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -3187,12 +3199,12 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-f53eab44dba8d43f</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -3207,9 +3219,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3219,17 +3231,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>235/26</t>
+          <t>499/26</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Licitación Privada N° 235/26: reparación de cenefas en losas pórticos</t>
+          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -3257,7 +3269,7 @@
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>id-22f9c51cdaebefb7</t>
+          <t>id-f53eab44dba8d43f</t>
         </is>
       </c>
     </row>
@@ -3284,17 +3296,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>498/26</t>
+          <t>235/26</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA N° 498/26: reparación de un tramo del cerramiento perimetral del Túnel Subfluvial</t>
+          <t>Licitación Privada N° 235/26: reparación de cenefas en losas pórticos</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -3322,12 +3334,272 @@
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
+          <t>id-22f9c51cdaebefb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Túnel Subfluvial</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>498/26</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>LICITACIÓN PÚBLICA N° 498/26: reparación de un tramo del cerramiento perimetral del Túnel Subfluvial</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Túnel Subfluvial</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
           <t>id-46d81e3efd2ae483</t>
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>10-2026</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego — figura como Pendiente</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>id-bdd0abb0374c3f42</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>09-2026</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego — figura como Pendiente</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>id-42c411be9946d956</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Licitación Privada</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>04-2026</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego — figura como Pendiente</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr"/>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>id-023b6b75e7014a9c</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O40"/>
+  <autoFilter ref="A1:O44"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3352,8 +3624,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId28"/>
@@ -3363,8 +3635,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId39"/>
@@ -3372,24 +3644,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId66"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +75,11 @@
         <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6D9F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -88,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -101,6 +106,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -466,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1104,18 +1110,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE ORO VERDE</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr"/>
+          <t>LICITACIÓN PÚBLICA</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>76/2026</t>
+        </is>
+      </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>El procedimiento licitatorio regido por el presente pliego tiene por objeto la Licitación Pública N° 03/2026 para la venta de los siguientes bienes municipales: a) MINI RETRO DE TIRO: Marca RICHIGER, Serie A, N° 101. Modelo N° 186. Motor N° 991023899, C. V 7, 50, Modelo 7, 50 DB, RPM 1.500 b) COLECTIVO: Mercedes Benz, dominio UKZ353, modelo 1977 según lo que s e detalla en el Pliego de Bases y Condiciones que forma parte de la presente como Anexo I</t>
+          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1125,7 +1135,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>La apertura de sobres se realizará el día 14 de septiembre del 2026 a las 10:00 horas, en la sede municipal</t>
+          <t>14-09-2026 08:00</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1133,11 +1143,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>El pliego será gratuito. El mismo se encontrará para su consulta y ent</t>
-        </is>
-      </c>
+      <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1150,12 +1156,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-ddc4dfb118d357f7</t>
+          <t>id-ccdfae2a7ede4696</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1183,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>MUNICIPALIDAD DE HERRERA — DPTO. URUGUAY, ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>76/2026</t>
+          <t>01-2026</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
+          <t>Adquisición de vehículo 0 km destinado al traslado de personas tipo van, con capacidad para 11 plazas (1 conductor + 10 pasajeros), motorización a nafta/diesel, según pliego de espec ificaciones técnicas</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>14-09-2026 08:00</t>
+          <t>DE LAS OFERTAS: el día 15/09/2026, a las 11:00 hs. en el Edificio Municipal de Herrera, sito en Av. H. Bozzolo, Nº 165,</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1210,7 +1216,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1223,12 +1233,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-ccdfae2a7ede4696</t>
+          <t>id-28313c7a9524d0ee</t>
         </is>
       </c>
     </row>
@@ -1243,14 +1253,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE HERRERA — DPTO. URUGUAY, ENTRE RÍOS</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1260,12 +1270,12 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>01-2026</t>
+          <t>014/2026</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de vehículo 0 km destinado al traslado de personas tipo van, con capacidad para 11 plazas (1 conductor + 10 pasajeros), motorización a nafta/diesel, según pliego de espec ificaciones técnicas</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1275,7 +1285,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 15/09/2026, a las 11:00 hs. en el Edificio Municipal de Herrera, sito en Av. H. Bozzolo, Nº 165,</t>
+          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1285,7 +1295,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -1305,7 +1315,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-28313c7a9524d0ee</t>
+          <t>id-9e58cc9ec0b69356</t>
         </is>
       </c>
     </row>
@@ -1320,14 +1330,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
+          <t>MINISTERIO DE PLANEAMIENTO E INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1337,12 +1347,12 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>014/2026</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “NUEVA INSTALACION ELECTRICA, CUBIERTA DE TECHO Y REFACCION DE BAÑOS ESCUELA Nº 1 “JOSE MARIA TEXIER” -SAN SALVADOR-DEPARTAMENTO SAN SALVADOR.”</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1352,7 +1362,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>DE LAS OFERTAS: el día 15 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1362,7 +1372,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -1382,7 +1392,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-9e58cc9ec0b69356</t>
+          <t>id-fb80c8ade7a8651d</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1414,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO E INFRAESTRUCTURA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1414,12 +1424,12 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “NUEVA INSTALACION ELECTRICA, CUBIERTA DE TECHO Y REFACCION DE BAÑOS ESCUELA Nº 1 “JOSE MARIA TEXIER” -SAN SALVADOR-DEPARTAMENTO SAN SALVADOR.”</t>
+          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1429,7 +1439,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 15 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1437,29 +1447,21 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K13" s="4" t="inlineStr"/>
       <c r="L13" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-fb80c8ade7a8651d</t>
+          <t>id-952aef4c115d8f12</t>
         </is>
       </c>
     </row>
@@ -1474,14 +1476,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1491,22 +1493,22 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>27/2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
+          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
+          <t>16 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1520,15 +1522,19 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-952aef4c115d8f12</t>
+          <t>id-608017f47f903d65</t>
         </is>
       </c>
     </row>
@@ -1543,14 +1549,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
+          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1560,22 +1566,22 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>27/2026</t>
+          <t>06/26</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
+          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>16 de septiembre de 2026 - Hora: 10:00</t>
+          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1583,7 +1589,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
+        </is>
+      </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1601,7 +1611,7 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-608017f47f903d65</t>
+          <t>id-9dbdaa6090d92bd4</t>
         </is>
       </c>
     </row>
@@ -1616,14 +1626,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
+          <t>MUNICIPALIDAD DE SEGUÍ</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1633,12 +1643,12 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>06/26</t>
+          <t>08-2026</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
+          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”. Apertura de Sobres 17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y entrega en Área de Suministro del Municipio, y también se podrá descargar en el Sitio Oficial Digital Municipal https://www.segui.gob.ar . Edgardo Muller, Presidente Municipal. ID:52321 - F.C. 04-00075716 3 v./03/09/2026</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1648,19 +1658,15 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
+          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1678,7 +1684,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-9dbdaa6090d92bd4</t>
+          <t>id-90c3d1f38f49418a</t>
         </is>
       </c>
     </row>
@@ -1693,14 +1699,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SEGUÍ</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1710,30 +1716,34 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>08-2026</t>
+          <t>015/2026</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”. Apertura de Sobres 17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y entrega en Área de Suministro del Municipio, y también se podrá descargar en el Sitio Oficial Digital Municipal https://www.segui.gob.ar . Edgardo Muller, Presidente Municipal. ID:52321 - F.C. 04-00075716 3 v./03/09/2026</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y</t>
+          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
+        </is>
+      </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1751,7 +1761,7 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-90c3d1f38f49418a</t>
+          <t>id-74dfdad7e5f9d048</t>
         </is>
       </c>
     </row>
@@ -1766,14 +1776,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1783,12 +1793,12 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>015/2026</t>
+          <t>09/26</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1798,7 +1808,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1808,7 +1818,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -1828,7 +1838,7 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-74dfdad7e5f9d048</t>
+          <t>id-6a4a84712fd41a03</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1860,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1860,12 +1870,12 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>09/26</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
+          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1875,7 +1885,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1883,29 +1893,21 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K19" s="4" t="inlineStr"/>
       <c r="L19" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M19" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-6a4a84712fd41a03</t>
+          <t>id-885d4847519dfd48</t>
         </is>
       </c>
     </row>
@@ -1920,14 +1922,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1935,24 +1937,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>09/2026</t>
-        </is>
-      </c>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1960,21 +1958,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Sin Cargo</t>
+        </is>
+      </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-885d4847519dfd48</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -1989,14 +1995,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2004,10 +2010,14 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez realizado el depósito/transferenci</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -2017,17 +2027,17 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN N</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>Sin Cargo</t>
+          <t>Habilitación: Pesos Ochenta Mil con 0/100 - $ 80.000, 00 - Habilitació</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -2047,7 +2057,7 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2079,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2079,12 +2089,12 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez realizado el depósito/transferenci</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -2094,7 +2104,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN N</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2104,7 +2114,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>Habilitación: Pesos Ochenta Mil con 0/100 - $ 80.000, 00 - Habilitació</t>
+          <t>Habilitación: Pesos Ciento Veinte Mil con 0/100 - $ 120.000, 00 - Habi</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -2124,7 +2134,7 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2156,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2156,32 +2166,32 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>Habilitación: Pesos Ciento Veinte Mil con 0/100 - $ 120.000, 00 - Habi</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
@@ -2201,7 +2211,7 @@
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2233,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2233,12 +2243,12 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -2248,7 +2258,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2256,29 +2266,21 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M24" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
@@ -2288,9 +2290,9 @@
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -2300,7 +2302,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2310,22 +2312,18 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2333,21 +2331,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2362,14 +2368,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2379,18 +2385,18 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2398,11 +2404,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K26" s="4" t="inlineStr"/>
       <c r="L26" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2420,7 +2422,7 @@
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -2508,35 +2510,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Boletín Oficial</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>ENERSA convoca a la Licitación Nº 2026- 1227 con el objeto de la provi sión de postes de hormigón para líneas</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2550,15 +2552,19 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-e90021854bcee649</t>
         </is>
       </c>
     </row>
@@ -2590,18 +2596,18 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>03/26</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2623,7 +2629,7 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
@@ -2655,18 +2661,18 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2688,7 +2694,7 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
@@ -2720,18 +2726,18 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2753,7 +2759,7 @@
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
@@ -2785,18 +2791,18 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2818,7 +2824,7 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
@@ -2848,16 +2854,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>06/2025</t>
+        </is>
+      </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2879,7 +2889,7 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
@@ -2909,20 +2919,16 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>04/2025</t>
-        </is>
-      </c>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2944,7 +2950,7 @@
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
@@ -2976,18 +2982,18 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3009,7 +3015,7 @@
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
@@ -3041,18 +3047,18 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3074,7 +3080,7 @@
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
@@ -3111,13 +3117,13 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3139,7 +3145,7 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -3161,28 +3167,28 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3199,12 +3205,12 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -3219,29 +3225,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>499/26</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -3264,12 +3270,12 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>id-f53eab44dba8d43f</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -3284,9 +3290,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3296,17 +3302,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>235/26</t>
+          <t>499/26</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Licitación Privada N° 235/26: reparación de cenefas en losas pórticos</t>
+          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -3334,7 +3340,7 @@
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>id-22f9c51cdaebefb7</t>
+          <t>id-f53eab44dba8d43f</t>
         </is>
       </c>
     </row>
@@ -3361,17 +3367,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>498/26</t>
+          <t>235/26</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA N° 498/26: reparación de un tramo del cerramiento perimetral del Túnel Subfluvial</t>
+          <t>Licitación Privada N° 235/26: reparación de cenefas en losas pórticos</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -3399,7 +3405,7 @@
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>id-46d81e3efd2ae483</t>
+          <t>id-22f9c51cdaebefb7</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3427,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3431,18 +3437,18 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>10-2026</t>
+          <t>498/26</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>LICITACIÓN PÚBLICA N° 498/26: reparación de un tramo del cerramiento perimetral del Túnel Subfluvial</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -3459,12 +3465,12 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-46d81e3efd2ae483</t>
         </is>
       </c>
     </row>
@@ -3479,35 +3485,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>09-2026</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -3524,12 +3530,12 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>id-42c411be9946d956</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
@@ -3556,17 +3562,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>10-2026</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -3594,12 +3600,142 @@
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
+          <t>id-bdd0abb0374c3f42</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>09-2026</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego — figura como Pendiente</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr"/>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>id-42c411be9946d956</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Licitación Privada</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>04-2026</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego — figura como Pendiente</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr"/>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
           <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O44"/>
+  <autoFilter ref="A1:O46"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3624,8 +3760,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId28"/>
@@ -3635,8 +3771,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId39"/>
@@ -3644,29 +3780,32 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId69"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1922,14 +1922,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1937,20 +1937,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>07/2026</t>
+        </is>
+      </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>21/09/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1960,7 +1964,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Sin Cargo</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -1980,7 +1984,7 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-6ddfa0f2f1aa296d</t>
         </is>
       </c>
     </row>
@@ -1995,14 +1999,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2010,14 +2014,10 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>10/2026</t>
-        </is>
-      </c>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez realizado el depósito/transferenci</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -2027,17 +2027,17 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN N</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>Habilitación: Pesos Ochenta Mil con 0/100 - $ 80.000, 00 - Habilitació</t>
+          <t>Sin Cargo</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez realizado el depósito/transferenci</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN N</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2112,11 +2112,7 @@
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Habilitación: Pesos Ciento Veinte Mil con 0/100 - $ 120.000, 00 - Habi</t>
-        </is>
-      </c>
+      <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2134,7 +2130,7 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2152,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2166,34 +2162,30 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2211,7 +2203,7 @@
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
@@ -2226,14 +2218,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2243,22 +2235,22 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCLUIDO</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2266,21 +2258,29 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -2290,9 +2290,9 @@
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2312,18 +2312,22 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr"/>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2333,7 +2337,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
@@ -2353,7 +2357,7 @@
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2363,19 +2367,19 @@
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2385,18 +2389,22 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr"/>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2410,19 +2418,15 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M26" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
@@ -2437,14 +2441,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2454,18 +2458,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2475,7 +2479,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>s in cargo Consultas: comprascomuna6to@hotmail.com Celular: 3444- 4493</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
@@ -2495,7 +2499,7 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2517,22 +2521,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Boletín Oficial</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>ENERSA convoca a la Licitación Nº 2026- 1227 con el objeto de la provi sión de postes de hormigón para líneas</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -2564,7 +2568,7 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-e90021854bcee649</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -2579,14 +2583,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2596,18 +2600,18 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2621,15 +2625,19 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2644,35 +2652,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Boletín Oficial</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>ENERSA convoca a la Licitación Nº 2026- 1227 con el objeto de la provi sión de postes de hormigón para líneas</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2686,15 +2694,19 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-e90021854bcee649</t>
         </is>
       </c>
     </row>
@@ -2726,18 +2738,18 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>03/26</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2759,7 +2771,7 @@
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
@@ -2791,18 +2803,18 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2824,7 +2836,7 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
@@ -2856,18 +2868,18 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2889,7 +2901,7 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
@@ -2919,16 +2931,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>05/2025</t>
+        </is>
+      </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2950,7 +2966,7 @@
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
@@ -2982,18 +2998,18 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>04/2025</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3015,7 +3031,7 @@
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
@@ -3045,20 +3061,16 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>03/2025</t>
-        </is>
-      </c>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3080,7 +3092,7 @@
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
@@ -3112,18 +3124,18 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3145,7 +3157,7 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
@@ -3177,18 +3189,18 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3210,7 +3222,7 @@
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
@@ -3232,28 +3244,28 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3270,12 +3282,12 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -3290,14 +3302,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3307,18 +3319,18 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>499/26</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -3335,12 +3347,12 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>id-f53eab44dba8d43f</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -3355,29 +3367,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>235/26</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Licitación Privada N° 235/26: reparación de cenefas en losas pórticos</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -3400,12 +3412,12 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>id-22f9c51cdaebefb7</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -3420,9 +3432,9 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3437,12 +3449,12 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>498/26</t>
+          <t>499/26</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA N° 498/26: reparación de un tramo del cerramiento perimetral del Túnel Subfluvial</t>
+          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -3470,7 +3482,7 @@
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>id-46d81e3efd2ae483</t>
+          <t>id-f53eab44dba8d43f</t>
         </is>
       </c>
     </row>
@@ -3485,29 +3497,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>235/26</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>Licitación Privada N° 235/26: reparación de cenefas en losas pórticos</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -3530,12 +3542,12 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-22f9c51cdaebefb7</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3569,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3567,18 +3579,18 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>10-2026</t>
+          <t>498/26</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>LICITACIÓN PÚBLICA N° 498/26: reparación de un tramo del cerramiento perimetral del Túnel Subfluvial</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -3595,12 +3607,12 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-46d81e3efd2ae483</t>
         </is>
       </c>
     </row>
@@ -3615,35 +3627,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>09-2026</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3660,12 +3672,12 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>id-42c411be9946d956</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
@@ -3692,17 +3704,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>10-2026</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -3730,12 +3742,142 @@
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
+          <t>id-bdd0abb0374c3f42</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>09-2026</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego — figura como Pendiente</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr"/>
+      <c r="L47" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>id-42c411be9946d956</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Licitación Privada</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>04-2026</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego — figura como Pendiente</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O48" s="4" t="inlineStr">
+        <is>
           <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O46"/>
+  <autoFilter ref="A1:O48"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3780,32 +3922,36 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId73"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -1453,7 +1453,11 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>Min. Planeamiento (provincia)</t>
@@ -1648,7 +1652,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”. Apertura de Sobres 17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y entrega en Área de Suministro del Municipio, y también se podrá descargar en el Sitio Oficial Digital Municipal https://www.segui.gob.ar . Edgardo Muller, Presidente Municipal. ID:52321 - F.C. 04-00075716 3 v./03/09/2026</t>
+          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1658,12 +1662,12 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal. El pliego será Gratuito. El mismo se encontrará para su consulta y</t>
+          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr"/>
@@ -1899,7 +1903,11 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>Min. Planeamiento (provincia)</t>
@@ -2094,7 +2102,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez realizado el depósito/transferenci</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -2104,7 +2112,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN N</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2167,7 +2175,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G. Apertura de Ofertas: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.- Venta de Pliegos - Habilitación a la Licitación: Desde el 03 de septiembre del año 2026 y hasta el día 17 de septiembre del año 2026, inclusive. Una vez</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -2177,7 +2185,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2418,7 +2426,11 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
           <t>Min. Planeamiento (provincia)</t>
@@ -2763,7 +2775,11 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>IAPV — Viviendas</t>
@@ -2828,7 +2844,11 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>IAPV — Viviendas</t>
@@ -2893,7 +2913,11 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>IAPV — Viviendas</t>
@@ -2958,7 +2982,11 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>IAPV — Viviendas</t>
@@ -3023,7 +3051,11 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
           <t>IAPV — Viviendas</t>
@@ -3084,7 +3116,11 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
           <t>IAPV — Viviendas</t>
@@ -3149,7 +3185,11 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
           <t>IAPV — Viviendas</t>
@@ -3214,7 +3254,11 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr">
         <is>
           <t>IAPV — Viviendas</t>
@@ -3279,7 +3323,11 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
           <t>IAPV — Viviendas</t>
@@ -3344,7 +3392,11 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
           <t>IAPV — Viviendas</t>
@@ -3409,7 +3461,11 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
           <t>Vialidad Entre Ríos (DPV)</t>
@@ -3474,7 +3530,11 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>Túnel Subfluvial</t>
@@ -3539,7 +3599,11 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
           <t>Túnel Subfluvial</t>
@@ -3604,7 +3668,11 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
           <t>Túnel Subfluvial</t>
@@ -3669,7 +3737,11 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
           <t>ENERSA</t>
@@ -3734,7 +3806,11 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr">
         <is>
           <t>CAFESG (Salto Grande)</t>
@@ -3799,7 +3875,11 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
+      <c r="M47" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr">
         <is>
           <t>CAFESG (Salto Grande)</t>
@@ -3864,7 +3944,11 @@
           <t>ver licitación</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
+      <c r="M48" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr">
         <is>
           <t>CAFESG (Salto Grande)</t>
@@ -3902,56 +3986,77 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId94"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -1670,7 +1670,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Gratuito</t>
+        </is>
+      </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -880,14 +880,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NOGOYA — COMUNA DISTRITO SAUCE -- NOGOYA</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -897,22 +897,22 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>499/26</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Convocar para la adquisi ción de un Tractor agrícola 0 km, con las siguientes características técnicas: potencia de motor de 130 a 150 HP; doble Tracción, 6 (seis) cilindros; y demás especificación que se encuentran en el pliego de Especificaciones Técnicas</t>
+          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Viernes 11 de Septiembre de 2026- a las 10:00 horas en la Sede Comunal de Comuna Distrito Sauce</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -920,11 +920,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sin costo. Solicitar en la Sede Comunal de Distrito Sauce Nogoya o al </t>
-        </is>
-      </c>
+      <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -937,12 +933,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-328f5a2f67c14702</t>
+          <t>id-f53eab44dba8d43f</t>
         </is>
       </c>
     </row>
@@ -964,22 +960,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>NOGOYA — COMUNA DISTRITO SAUCE -- NOGOYA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>77/2026</t>
+          <t>1/26</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>ADQUISICION DE CAMIONETAS</t>
+          <t>Convocar para la adquisi ción de un Tractor agrícola 0 km, con las siguientes características técnicas: potencia de motor de 130 a 150 HP; doble Tracción, 6 (seis) cilindros; y demás especificación que se encuentran en el pliego de Especificaciones Técnicas</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -989,7 +985,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>11-09-2026 08:00</t>
+          <t>Viernes 11 de Septiembre de 2026- a las 10:00 horas en la Sede Comunal de Comuna Distrito Sauce</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -997,7 +993,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sin costo. Solicitar en la Sede Comunal de Distrito Sauce Nogoya o al </t>
+        </is>
+      </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-dff70529581309e6</t>
+          <t>id-328f5a2f67c14702</t>
         </is>
       </c>
     </row>
@@ -1030,39 +1030,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>77/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, C ondiciones Particulares y demás documentación</t>
+          <t>ADQUISICION DE CAMIONETAS</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>14 de septiembre de 2026 - Hora: 10:00</t>
+          <t>11-09-2026 08:00</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1083,12 +1083,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-85e6cfd11c8a8889</t>
+          <t>id-dff70529581309e6</t>
         </is>
       </c>
     </row>
@@ -1103,29 +1103,29 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>76/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
+          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, C ondiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>14-09-2026 08:00</t>
+          <t>14 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-ccdfae2a7ede4696</t>
+          <t>id-85e6cfd11c8a8889</t>
         </is>
       </c>
     </row>
@@ -1183,32 +1183,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE HERRERA — DPTO. URUGUAY, ENTRE RÍOS</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>01-2026</t>
+          <t>76/2026</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de vehículo 0 km destinado al traslado de personas tipo van, con capacidad para 11 plazas (1 conductor + 10 pasajeros), motorización a nafta/diesel, según pliego de espec ificaciones técnicas</t>
+          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 15/09/2026, a las 11:00 hs. en el Edificio Municipal de Herrera, sito en Av. H. Bozzolo, Nº 165,</t>
+          <t>14-09-2026 08:00</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1216,11 +1216,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1233,12 +1229,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-28313c7a9524d0ee</t>
+          <t>id-ccdfae2a7ede4696</t>
         </is>
       </c>
     </row>
@@ -1253,14 +1249,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
+          <t>MUNICIPALIDAD DE HERRERA — DPTO. URUGUAY, ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1270,12 +1266,12 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>014/2026</t>
+          <t>01-2026</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
+          <t>Adquisición de vehículo 0 km destinado al traslado de personas tipo van, con capacidad para 11 plazas (1 conductor + 10 pasajeros), motorización a nafta/diesel, según pliego de espec ificaciones técnicas</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1285,7 +1281,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>DE LAS OFERTAS: el día 15/09/2026, a las 11:00 hs. en el Edificio Municipal de Herrera, sito en Av. H. Bozzolo, Nº 165,</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1295,7 +1291,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -1315,7 +1311,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-9e58cc9ec0b69356</t>
+          <t>id-28313c7a9524d0ee</t>
         </is>
       </c>
     </row>
@@ -1330,14 +1326,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO E INFRAESTRUCTURA</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1347,12 +1343,12 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>014/2026</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “NUEVA INSTALACION ELECTRICA, CUBIERTA DE TECHO Y REFACCION DE BAÑOS ESCUELA Nº 1 “JOSE MARIA TEXIER” -SAN SALVADOR-DEPARTAMENTO SAN SALVADOR.”</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1362,7 +1358,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 15 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1372,7 +1368,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -1392,7 +1388,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-fb80c8ade7a8651d</t>
+          <t>id-9e58cc9ec0b69356</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1410,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>MINISTERIO DE PLANEAMIENTO E INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1424,12 +1420,12 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “NUEVA INSTALACION ELECTRICA, CUBIERTA DE TECHO Y REFACCION DE BAÑOS ESCUELA Nº 1 “JOSE MARIA TEXIER” -SAN SALVADOR-DEPARTAMENTO SAN SALVADOR.”</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1439,7 +1435,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
+          <t>DE LAS OFERTAS: el día 15 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1447,7 +1443,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-952aef4c115d8f12</t>
+          <t>id-fb80c8ade7a8651d</t>
         </is>
       </c>
     </row>
@@ -1480,14 +1480,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1497,22 +1497,22 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>27/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
+          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>16 de septiembre de 2026 - Hora: 10:00</t>
+          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-608017f47f903d65</t>
+          <t>id-952aef4c115d8f12</t>
         </is>
       </c>
     </row>
@@ -1553,14 +1553,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1570,22 +1570,22 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>06/26</t>
+          <t>27/2026</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
+          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
+          <t>16 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1593,11 +1593,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
-        </is>
-      </c>
+      <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1615,7 +1611,7 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-9dbdaa6090d92bd4</t>
+          <t>id-608017f47f903d65</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1633,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SEGUÍ</t>
+          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1647,12 +1643,12 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>08-2026</t>
+          <t>06/26</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
+          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1662,7 +1658,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
+          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1672,7 +1668,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Gratuito</t>
+          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -1692,7 +1688,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-90c3d1f38f49418a</t>
+          <t>id-9dbdaa6090d92bd4</t>
         </is>
       </c>
     </row>
@@ -1707,14 +1703,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>MUNICIPALIDAD DE SEGUÍ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1724,22 +1720,22 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>015/2026</t>
+          <t>08-2026</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
+          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1749,7 +1745,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
+          <t>Gratuito</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
@@ -1769,7 +1765,7 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-74dfdad7e5f9d048</t>
+          <t>id-90c3d1f38f49418a</t>
         </is>
       </c>
     </row>
@@ -1784,14 +1780,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1801,12 +1797,12 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>09/26</t>
+          <t>015/2026</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1816,7 +1812,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1826,7 +1822,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -1846,7 +1842,7 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-6a4a84712fd41a03</t>
+          <t>id-74dfdad7e5f9d048</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1864,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1878,12 +1874,12 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>09/26</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1893,7 +1889,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1901,7 +1897,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1914,12 +1914,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-885d4847519dfd48</t>
+          <t>id-6a4a84712fd41a03</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1951,22 +1951,22 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
+          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026 HORA: 10:00 HS</t>
+          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1974,11 +1974,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K20" s="4" t="inlineStr"/>
       <c r="L20" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1991,12 +1987,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-6ddfa0f2f1aa296d</t>
+          <t>id-885d4847519dfd48</t>
         </is>
       </c>
     </row>
@@ -2011,14 +2007,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2026,20 +2022,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>07/2026</t>
+        </is>
+      </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>21/09/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>Sin Cargo</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-6ddfa0f2f1aa296d</t>
         </is>
       </c>
     </row>
@@ -2084,14 +2084,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2099,14 +2099,10 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>10/2026</t>
-        </is>
-      </c>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -2116,15 +2112,19 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Sin Cargo</t>
+        </is>
+      </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
@@ -2230,14 +2230,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2247,34 +2247,30 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCLUIDO</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2292,7 +2288,7 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
@@ -2307,14 +2303,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2324,22 +2320,22 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCLUIDO</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2349,7 +2345,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
@@ -2369,7 +2365,7 @@
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2387,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2401,12 +2397,12 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2416,7 +2412,7 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2424,7 +2420,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2452,9 +2452,9 @@
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2474,18 +2474,22 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr"/>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2493,11 +2497,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K27" s="4" t="inlineStr"/>
       <c r="L27" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2510,12 +2510,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
@@ -2530,14 +2530,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2547,18 +2547,18 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2566,7 +2566,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2584,7 +2588,7 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2599,14 +2603,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2616,12 +2620,12 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -2653,7 +2657,7 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -2668,29 +2672,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Boletín Oficial</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>ENERSA convoca a la Licitación Nº 2026- 1227 con el objeto de la provi sión de postes de hormigón para líneas</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -2722,7 +2726,7 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-e90021854bcee649</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2737,35 +2741,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Boletín Oficial</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>ENERSA convoca a la Licitación Nº 2026- 1227 con el objeto de la provi sión de postes de hormigón para líneas</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2786,12 +2790,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-e90021854bcee649</t>
         </is>
       </c>
     </row>
@@ -2823,18 +2827,18 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>03/26</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2860,7 +2864,7 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
@@ -2892,18 +2896,18 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2929,7 +2933,7 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
@@ -2961,18 +2965,18 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2998,7 +3002,7 @@
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
@@ -3030,18 +3034,18 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3067,7 +3071,7 @@
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
@@ -3097,16 +3101,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>06/2025</t>
+        </is>
+      </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3132,7 +3140,7 @@
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
@@ -3162,20 +3170,16 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>04/2025</t>
-        </is>
-      </c>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3201,7 +3205,7 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
@@ -3233,18 +3237,18 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3270,7 +3274,7 @@
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
@@ -3302,18 +3306,18 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3339,7 +3343,7 @@
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
@@ -3376,13 +3380,13 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -3408,7 +3412,7 @@
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -3430,28 +3434,28 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -3472,12 +3476,12 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -3492,29 +3496,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>499/26</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -3541,12 +3545,12 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>id-f53eab44dba8d43f</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -3561,29 +3565,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>235/26</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Licitación Privada N° 235/26: reparación de cenefas en losas pórticos</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -3610,12 +3614,12 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>id-22f9c51cdaebefb7</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3641,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3647,18 +3651,18 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>498/26</t>
+          <t>10-2026</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA N° 498/26: reparación de un tramo del cerramiento perimetral del Túnel Subfluvial</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -3679,12 +3683,12 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>id-46d81e3efd2ae483</t>
+          <t>id-bdd0abb0374c3f42</t>
         </is>
       </c>
     </row>
@@ -3699,35 +3703,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C45" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>09-2026</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3748,12 +3752,12 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-42c411be9946d956</t>
         </is>
       </c>
     </row>
@@ -3780,17 +3784,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>10-2026</t>
+          <t>04-2026</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -3822,150 +3826,12 @@
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>09-2026</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr"/>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego — figura como Pendiente</t>
-        </is>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K47" s="4" t="inlineStr"/>
-      <c r="L47" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M47" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="O47" s="4" t="inlineStr">
-        <is>
-          <t>id-42c411be9946d956</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Licitación Privada</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>04-2026</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr"/>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego — figura como Pendiente</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K48" s="4" t="inlineStr"/>
-      <c r="L48" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M48" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="O48" s="4" t="inlineStr">
-        <is>
           <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O48"/>
+  <autoFilter ref="A1:O46"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -4057,10 +3923,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId94"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2827,18 +2827,18 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2846,7 +2846,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>$ 120.976,01 CUENTA DE DEPÓSITO: NBersa CC $ 00010</t>
+        </is>
+      </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2864,7 +2868,7 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -2896,18 +2900,18 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2933,7 +2937,7 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -2955,28 +2959,28 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2997,12 +3001,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
@@ -3017,35 +3021,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3066,12 +3070,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
@@ -3086,14 +3090,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3103,18 +3107,18 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>10-2026</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3135,12 +3139,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-bdd0abb0374c3f42</t>
         </is>
       </c>
     </row>
@@ -3155,14 +3159,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3170,16 +3174,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>09-2026</t>
+        </is>
+      </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3200,12 +3208,12 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-42c411be9946d956</t>
         </is>
       </c>
     </row>
@@ -3220,35 +3228,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>04/2025</t>
+          <t>04-2026</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3269,569 +3277,17 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>IAPV (Vivienda)</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>03/2025</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr"/>
-      <c r="L39" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M39" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>IAPV — Viviendas</t>
-        </is>
-      </c>
-      <c r="O39" s="4" t="inlineStr">
-        <is>
-          <t>id-75bfffae63b7eedc</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>IAPV (Vivienda)</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr"/>
-      <c r="L40" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M40" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>IAPV — Viviendas</t>
-        </is>
-      </c>
-      <c r="O40" s="4" t="inlineStr">
-        <is>
-          <t>id-07ddb93a12c5a870</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>IAPV (Vivienda)</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>Concurso de Precio N° 02/2025</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr"/>
-      <c r="L41" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M41" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>IAPV — Viviendas</t>
-        </is>
-      </c>
-      <c r="O41" s="4" t="inlineStr">
-        <is>
-          <t>id-7c1bf02160a66f67</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Concurso</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>01/26</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M42" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
-        </is>
-      </c>
-      <c r="O42" s="4" t="inlineStr">
-        <is>
-          <t>id-9a16884dd5a64a49</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>ENERSA</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Licitación</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>2026-1227</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr"/>
-      <c r="L43" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M43" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>ENERSA</t>
-        </is>
-      </c>
-      <c r="O43" s="4" t="inlineStr">
-        <is>
-          <t>id-0691eb485d7548eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>10-2026</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr"/>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego — figura como Pendiente</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr"/>
-      <c r="L44" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M44" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="O44" s="4" t="inlineStr">
-        <is>
-          <t>id-bdd0abb0374c3f42</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>09-2026</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr"/>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego — figura como Pendiente</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K45" s="4" t="inlineStr"/>
-      <c r="L45" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M45" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="O45" s="4" t="inlineStr">
-        <is>
-          <t>id-42c411be9946d956</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Licitación Privada</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>04-2026</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr"/>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego — figura como Pendiente</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K46" s="4" t="inlineStr"/>
-      <c r="L46" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M46" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="O46" s="4" t="inlineStr">
-        <is>
           <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O46"/>
+  <autoFilter ref="A1:O38"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3907,22 +3363,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId90"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -2848,7 +2848,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>$ 120.976,01 CUENTA DE DEPÓSITO: NBersa CC $ 00010</t>
+          <t>$ 120.976,01</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -657,14 +657,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FEDERACION — COMUNA DE SAN PEDRO -- DEPARTAMENTO DE FEDERACIÓN</t>
+          <t>CONCORDIA — MUNICIPALIDAD DE PUERTO YERUA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>1/2026</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION RIPIO SELECCIONADO EN ORIGEN Y ENTREGADO SOBRE TRANSPORTE”</t>
+          <t>Adquisición de una motoniveladora 0 Km</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>09 de Septiembre de 2026 - 10:00 hs</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -697,11 +697,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>Sin costo</t>
-        </is>
-      </c>
+      <c r="K3" s="4" t="inlineStr"/>
       <c r="L3" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -719,7 +715,7 @@
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>id-719cc55444d8579b</t>
+          <t>id-61b6e4f9568150b0</t>
         </is>
       </c>
     </row>
@@ -734,14 +730,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CONCORDIA — MUNICIPALIDAD DE PUERTO YERUA</t>
+          <t>ENTE INTERPROVINCIAL TUNEL SUBFLUVIAL RAUL URANGA -- CARLOS S. BEGNIS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -749,14 +745,10 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1/2026</t>
-        </is>
-      </c>
+      <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de una motoniveladora 0 Km</t>
+          <t>EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -774,7 +766,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>GRATUITO FECHA DE APERTURA: 10/09/2026</t>
+        </is>
+      </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -792,7 +788,7 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>id-61b6e4f9568150b0</t>
+          <t>id-439ddd7aaa7f7b3e</t>
         </is>
       </c>
     </row>
@@ -814,7 +810,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ENTE INTERPROVINCIAL TUNEL SUBFLUVIAL RAUL URANGA -- CARLOS S. BEGNIS</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -822,10 +818,14 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>499/26</t>
+        </is>
+      </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
+          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>10/09/26</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -843,11 +843,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>GRATUITO FECHA DE APERTURA: 10/09/2026</t>
-        </is>
-      </c>
+      <c r="K5" s="4" t="inlineStr"/>
       <c r="L5" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -860,12 +856,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Túnel Subfluvial</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>id-439ddd7aaa7f7b3e</t>
+          <t>id-f53eab44dba8d43f</t>
         </is>
       </c>
     </row>
@@ -880,14 +876,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>NOGOYA — COMUNA DISTRITO SAUCE -- NOGOYA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -897,22 +893,22 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>499/26</t>
+          <t>1/26</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
+          <t>Convocar para la adquisi ción de un Tractor agrícola 0 km, con las siguientes características técnicas: potencia de motor de 130 a 150 HP; doble Tracción, 6 (seis) cilindros; y demás especificación que se encuentran en el pliego de Especificaciones Técnicas</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>10/09/26</t>
+          <t>Viernes 11 de Septiembre de 2026- a las 10:00 horas en la Sede Comunal de Comuna Distrito Sauce</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -920,7 +916,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sin costo. Solicitar en la Sede Comunal de Distrito Sauce Nogoya o al </t>
+        </is>
+      </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -933,12 +933,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-f53eab44dba8d43f</t>
+          <t>id-328f5a2f67c14702</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NOGOYA — COMUNA DISTRITO SAUCE -- NOGOYA</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>77/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Convocar para la adquisi ción de un Tractor agrícola 0 km, con las siguientes características técnicas: potencia de motor de 130 a 150 HP; doble Tracción, 6 (seis) cilindros; y demás especificación que se encuentran en el pliego de Especificaciones Técnicas</t>
+          <t>ADQUISICION DE CAMIONETAS</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Viernes 11 de Septiembre de 2026- a las 10:00 horas en la Sede Comunal de Comuna Distrito Sauce</t>
+          <t>11-09-2026 08:00</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -993,11 +993,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sin costo. Solicitar en la Sede Comunal de Distrito Sauce Nogoya o al </t>
-        </is>
-      </c>
+      <c r="K7" s="4" t="inlineStr"/>
       <c r="L7" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1010,12 +1006,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-328f5a2f67c14702</t>
+          <t>id-dff70529581309e6</t>
         </is>
       </c>
     </row>
@@ -1030,39 +1026,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Áridos</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>77/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>ADQUISICION DE CAMIONETAS</t>
+          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, C ondiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>11-09-2026 08:00</t>
+          <t>14 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1083,12 +1079,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-dff70529581309e6</t>
+          <t>id-85e6cfd11c8a8889</t>
         </is>
       </c>
     </row>
@@ -1103,29 +1099,29 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>76/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, C ondiciones Particulares y demás documentación</t>
+          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1135,7 +1131,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>14 de septiembre de 2026 - Hora: 10:00</t>
+          <t>14-09-2026 08:00</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1156,12 +1152,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-85e6cfd11c8a8889</t>
+          <t>id-ccdfae2a7ede4696</t>
         </is>
       </c>
     </row>
@@ -1183,32 +1179,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>MUNICIPALIDAD DE HERRERA — DPTO. URUGUAY, ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>76/2026</t>
+          <t>01-2026</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
+          <t>Adquisición de vehículo 0 km destinado al traslado de personas tipo van, con capacidad para 11 plazas (1 conductor + 10 pasajeros), motorización a nafta/diesel, según pliego de espec ificaciones técnicas</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>14-09-2026 08:00</t>
+          <t>DE LAS OFERTAS: el día 15/09/2026, a las 11:00 hs. en el Edificio Municipal de Herrera, sito en Av. H. Bozzolo, Nº 165,</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1216,7 +1212,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-ccdfae2a7ede4696</t>
+          <t>id-28313c7a9524d0ee</t>
         </is>
       </c>
     </row>
@@ -1249,14 +1249,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE HERRERA — DPTO. URUGUAY, ENTRE RÍOS</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>01-2026</t>
+          <t>014/2026</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de vehículo 0 km destinado al traslado de personas tipo van, con capacidad para 11 plazas (1 conductor + 10 pasajeros), motorización a nafta/diesel, según pliego de espec ificaciones técnicas</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 15/09/2026, a las 11:00 hs. en el Edificio Municipal de Herrera, sito en Av. H. Bozzolo, Nº 165,</t>
+          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-28313c7a9524d0ee</t>
+          <t>id-9e58cc9ec0b69356</t>
         </is>
       </c>
     </row>
@@ -1326,14 +1326,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
+          <t>MINISTERIO DE PLANEAMIENTO E INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>014/2026</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “NUEVA INSTALACION ELECTRICA, CUBIERTA DE TECHO Y REFACCION DE BAÑOS ESCUELA Nº 1 “JOSE MARIA TEXIER” -SAN SALVADOR-DEPARTAMENTO SAN SALVADOR.”</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>DE LAS OFERTAS: el día 15 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-9e58cc9ec0b69356</t>
+          <t>id-fb80c8ade7a8651d</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO E INFRAESTRUCTURA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1420,12 +1420,12 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “NUEVA INSTALACION ELECTRICA, CUBIERTA DE TECHO Y REFACCION DE BAÑOS ESCUELA Nº 1 “JOSE MARIA TEXIER” -SAN SALVADOR-DEPARTAMENTO SAN SALVADOR.”</t>
+          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 15 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1443,11 +1443,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K13" s="4" t="inlineStr"/>
       <c r="L13" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1460,12 +1456,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-fb80c8ade7a8651d</t>
+          <t>id-952aef4c115d8f12</t>
         </is>
       </c>
     </row>
@@ -1480,14 +1476,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1497,22 +1493,22 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>27/2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
+          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
+          <t>16 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1533,12 +1529,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-952aef4c115d8f12</t>
+          <t>id-608017f47f903d65</t>
         </is>
       </c>
     </row>
@@ -1553,14 +1549,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
+          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1570,22 +1566,22 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>27/2026</t>
+          <t>06/26</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
+          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>16 de septiembre de 2026 - Hora: 10:00</t>
+          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1593,7 +1589,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
+        </is>
+      </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-608017f47f903d65</t>
+          <t>id-9dbdaa6090d92bd4</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
+          <t>MUNICIPALIDAD DE SEGUÍ</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>06/26</t>
+          <t>08-2026</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
+          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
+          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
+          <t>Gratuito</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-9dbdaa6090d92bd4</t>
+          <t>id-90c3d1f38f49418a</t>
         </is>
       </c>
     </row>
@@ -1703,14 +1703,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SEGUÍ</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1720,22 +1720,22 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>08-2026</t>
+          <t>015/2026</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
+          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Gratuito</t>
+          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-90c3d1f38f49418a</t>
+          <t>id-74dfdad7e5f9d048</t>
         </is>
       </c>
     </row>
@@ -1780,14 +1780,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>015/2026</t>
+          <t>09/26</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-74dfdad7e5f9d048</t>
+          <t>id-6a4a84712fd41a03</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>09/26</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
+          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1897,11 +1897,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K19" s="4" t="inlineStr"/>
       <c r="L19" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1914,12 +1910,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-6a4a84712fd41a03</t>
+          <t>id-885d4847519dfd48</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1937,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1951,22 +1947,22 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>21/09/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1974,7 +1970,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1987,12 +1987,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-885d4847519dfd48</t>
+          <t>id-6ddfa0f2f1aa296d</t>
         </is>
       </c>
     </row>
@@ -2007,14 +2007,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2022,24 +2022,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>07/2026</t>
-        </is>
-      </c>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026 HORA: 10:00 HS</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2049,7 +2045,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>Sin Cargo</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -2069,7 +2065,7 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-6ddfa0f2f1aa296d</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -2084,14 +2080,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2099,10 +2095,14 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>10/2026</t>
+        </is>
+      </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -2112,19 +2112,15 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Sin Cargo</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2142,7 +2138,7 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2160,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2174,12 +2170,12 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -2189,7 +2185,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2215,7 +2211,7 @@
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
@@ -2230,14 +2226,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2247,30 +2243,34 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCLUIDO</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -2303,14 +2303,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2320,22 +2320,22 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCLUIDO</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$ 100 (Cien)</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2420,11 +2420,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K26" s="4" t="inlineStr"/>
       <c r="L26" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2437,12 +2433,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
@@ -2452,9 +2448,9 @@
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -2464,7 +2460,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2474,22 +2470,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2497,7 +2489,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2510,12 +2506,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2530,14 +2526,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2547,18 +2543,18 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2566,11 +2562,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2588,7 +2580,7 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -2603,14 +2595,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2620,12 +2612,12 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -2657,7 +2649,7 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2672,29 +2664,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>Boletín Oficial</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>ENERSA convoca a la Licitación Nº 2026- 1227 con el objeto de la provi sión de postes de hormigón para líneas</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -2726,14 +2718,14 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-e90021854bcee649</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2741,35 +2733,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Boletín Oficial</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>03/26</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>ENERSA convoca a la Licitación Nº 2026- 1227 con el objeto de la provi sión de postes de hormigón para líneas</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2790,19 +2782,19 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-e90021854bcee649</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2827,18 +2819,18 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2846,11 +2838,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>$ 120.976,01</t>
-        </is>
-      </c>
+      <c r="K32" s="4" t="inlineStr"/>
       <c r="L32" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2868,14 +2856,14 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2900,18 +2888,18 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2937,14 +2925,14 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2959,28 +2947,28 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -3001,19 +2989,19 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3021,35 +3009,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3070,19 +3058,19 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3090,14 +3078,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3105,20 +3093,16 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>10-2026</t>
-        </is>
-      </c>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3139,19 +3123,19 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3159,14 +3143,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3176,18 +3160,18 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>09-2026</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3208,19 +3192,19 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-42c411be9946d956</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3228,35 +3212,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3277,17 +3261,500 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
+          <t>IAPV — Viviendas</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>id-75bfffae63b7eedc</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>IAPV (Vivienda)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Publicada 06/10/2025 — ver pliego</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr"/>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>IAPV — Viviendas</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>id-07ddb93a12c5a870</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>IAPV (Vivienda)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>02/2025</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Concurso de Precio N° 02/2025</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Publicada 19/06/2025 — ver pliego</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr"/>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>IAPV — Viviendas</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>id-7c1bf02160a66f67</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Vialidad Entre Ríos (DPV)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Concurso</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>01/26</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Vialidad Entre Ríos (DPV)</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>id-9a16884dd5a64a49</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ENERSA</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>2026-1227</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>ENERSA</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>id-0691eb485d7548eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
-      <c r="O38" s="4" t="inlineStr">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>10-2026</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego — figura como Pendiente</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>id-bdd0abb0374c3f42</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>09-2026</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego — figura como Pendiente</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr"/>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>id-42c411be9946d956</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Licitación Privada</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>04-2026</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego — figura como Pendiente</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr"/>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M45" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O45" s="4" t="inlineStr">
         <is>
           <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O38"/>
+  <autoFilter ref="A1:O45"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3363,6 +3830,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, C ondiciones Particulares y demás documentación</t>
+          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE HERRERA — DPTO. URUGUAY, ENTRE RÍOS</t>
+          <t>MUNICIPALIDAD DE HERRERA — DPTO. URUGUAY, ENTRE RIOS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de vehículo 0 km destinado al traslado de personas tipo van, con capacidad para 11 plazas (1 conductor + 10 pasajeros), motorización a nafta/diesel, según pliego de espec ificaciones técnicas</t>
+          <t>Adquisición de vehículo 0 km destinado al traslado de personas tipo van, con capacidad para 11 plazas (1 conductor + 10 pasajeros), motorización a nafta/diesel, según pliego de especificaciones técnicas</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2226,49 +2226,49 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCLUIDO</t>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$25.000,00</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
@@ -2303,14 +2303,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2320,22 +2320,22 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2420,7 +2420,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2433,12 +2437,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2448,9 +2452,9 @@
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -2460,7 +2464,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2470,18 +2474,22 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr"/>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2489,11 +2497,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K27" s="4" t="inlineStr"/>
       <c r="L27" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2506,12 +2510,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
@@ -2526,14 +2530,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2543,18 +2547,18 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2562,7 +2566,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>SIN COSTO</t>
+        </is>
+      </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2580,7 +2588,7 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2595,14 +2603,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2612,12 +2620,12 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -2649,7 +2657,7 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -2664,29 +2672,29 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Boletín Oficial</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>ENERSA convoca a la Licitación Nº 2026- 1227 con el objeto de la provi sión de postes de hormigón para líneas</t>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -2718,14 +2726,14 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-e90021854bcee649</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2733,35 +2741,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Boletín Oficial</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>ENERSA convoca a la Licitación Nº 2026- 1227 con el objeto de la provi sión de postes de hormigón para líneas</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2782,19 +2790,19 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-e90021854bcee649</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2819,18 +2827,18 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2838,7 +2846,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>$ 120.976,01</t>
+        </is>
+      </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2856,14 +2868,14 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2888,18 +2900,18 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2925,14 +2937,14 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2947,28 +2959,28 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2989,19 +3001,19 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3009,35 +3021,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3058,19 +3070,19 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3078,14 +3090,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3093,16 +3105,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>10-2026</t>
+        </is>
+      </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3123,19 +3139,19 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
+          <t>id-bdd0abb0374c3f42</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3143,14 +3159,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3160,18 +3176,18 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>04/2025</t>
+          <t>09-2026</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
+          <t>REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3192,19 +3208,19 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-34c85bcdb9b1123f</t>
+          <t>id-42c411be9946d956</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3212,35 +3228,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación Privada</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>03/2025</t>
+          <t>04-2026</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3261,500 +3277,17 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>id-75bfffae63b7eedc</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>IAPV (Vivienda)</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr"/>
-      <c r="L39" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M39" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>IAPV — Viviendas</t>
-        </is>
-      </c>
-      <c r="O39" s="4" t="inlineStr">
-        <is>
-          <t>id-07ddb93a12c5a870</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>IAPV (Vivienda)</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>Concurso de Precio N° 02/2025</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr"/>
-      <c r="L40" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M40" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>IAPV — Viviendas</t>
-        </is>
-      </c>
-      <c r="O40" s="4" t="inlineStr">
-        <is>
-          <t>id-7c1bf02160a66f67</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Concurso</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>01/26</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr"/>
-      <c r="L41" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M41" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
-        </is>
-      </c>
-      <c r="O41" s="4" t="inlineStr">
-        <is>
-          <t>id-9a16884dd5a64a49</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C42" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>ENERSA</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Licitación</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>2026-1227</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M42" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>ENERSA</t>
-        </is>
-      </c>
-      <c r="O42" s="4" t="inlineStr">
-        <is>
-          <t>id-0691eb485d7548eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>10-2026</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego — figura como Pendiente</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr"/>
-      <c r="L43" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M43" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="O43" s="4" t="inlineStr">
-        <is>
-          <t>id-bdd0abb0374c3f42</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>09-2026</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr"/>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego — figura como Pendiente</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr"/>
-      <c r="L44" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M44" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="O44" s="4" t="inlineStr">
-        <is>
-          <t>id-42c411be9946d956</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Licitación Privada</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>04-2026</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr"/>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego — figura como Pendiente</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K45" s="4" t="inlineStr"/>
-      <c r="L45" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M45" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="O45" s="4" t="inlineStr">
-        <is>
           <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O45"/>
+  <autoFilter ref="A1:O38"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3830,20 +3363,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CONCORDIA — MUNICIPALIDAD DE PUERTO YERUA</t>
+          <t>NOGOYA — COMUNA DISTRITO SAUCE -- NOGOYA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>1/2026</t>
+          <t>1/26</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de una motoniveladora 0 Km</t>
+          <t>Convocar para la adquisi ción de un Tractor agrícola 0 km, con las siguientes características técnicas: potencia de motor de 130 a 150 HP; doble Tracción, 6 (seis) cilindros; y demás especificación que se encuentran en el pliego de Especificaciones Técnicas</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>Viernes 11 de Septiembre de 2026- a las 10:00 horas en la Sede Comunal de Comuna Distrito Sauce</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -697,7 +697,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sin costo. Solicitar en la Sede Comunal de Distrito Sauce Nogoya o al </t>
+        </is>
+      </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -715,7 +719,7 @@
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>id-61b6e4f9568150b0</t>
+          <t>id-328f5a2f67c14702</t>
         </is>
       </c>
     </row>
@@ -737,7 +741,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ENTE INTERPROVINCIAL TUNEL SUBFLUVIAL RAUL URANGA -- CARLOS S. BEGNIS</t>
+          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -745,20 +749,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>06/2026</t>
+        </is>
+      </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
+          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -766,11 +774,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>GRATUITO FECHA DE APERTURA: 10/09/2026</t>
-        </is>
-      </c>
+      <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -788,7 +792,7 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>id-439ddd7aaa7f7b3e</t>
+          <t>id-85e6cfd11c8a8889</t>
         </is>
       </c>
     </row>
@@ -803,39 +807,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>LICITACIÓN PÚBLICA</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>499/26</t>
+          <t>76/2026</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA Nº 499/26: EXTRACCIÓN DE DEPÓSITOS DE SUELO EN SECTOR INFERIOR DEL TÚNEL SUBFLUVIAL</t>
+          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>10/09/26</t>
+          <t>14-09-2026 08:00</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -856,12 +860,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Túnel Subfluvial</t>
+          <t>Municipalidad de Paraná</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>id-f53eab44dba8d43f</t>
+          <t>id-ccdfae2a7ede4696</t>
         </is>
       </c>
     </row>
@@ -883,7 +887,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NOGOYA — COMUNA DISTRITO SAUCE -- NOGOYA</t>
+          <t>MUNICIPALIDAD DE HERRERA — DPTO. URUGUAY, ENTRE RIOS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -893,22 +897,22 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>01-2026</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Convocar para la adquisi ción de un Tractor agrícola 0 km, con las siguientes características técnicas: potencia de motor de 130 a 150 HP; doble Tracción, 6 (seis) cilindros; y demás especificación que se encuentran en el pliego de Especificaciones Técnicas</t>
+          <t>Adquisición de vehículo 0 km destinado al traslado de personas tipo van, con capacidad para 11 plazas (1 conductor + 10 pasajeros), motorización a nafta/diesel, según pliego de especificaciones técnicas</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Viernes 11 de Septiembre de 2026- a las 10:00 horas en la Sede Comunal de Comuna Distrito Sauce</t>
+          <t>DE LAS OFERTAS: el día 15/09/2026, a las 11:00 hs. en el Edificio Municipal de Herrera, sito en Av. H. Bozzolo, Nº 165,</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -918,7 +922,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sin costo. Solicitar en la Sede Comunal de Distrito Sauce Nogoya o al </t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -938,7 +942,7 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>id-328f5a2f67c14702</t>
+          <t>id-28313c7a9524d0ee</t>
         </is>
       </c>
     </row>
@@ -953,39 +957,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>77/2026</t>
+          <t>014/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>ADQUISICION DE CAMIONETAS</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>11-09-2026 08:00</t>
+          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -993,7 +997,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
+        </is>
+      </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1006,12 +1014,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>id-dff70529581309e6</t>
+          <t>id-9e58cc9ec0b69356</t>
         </is>
       </c>
     </row>
@@ -1026,14 +1034,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Áridos</t>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SAN SALVADOR — COMUNA COLONIA BAYLINA</t>
+          <t>MINISTERIO DE PLANEAMIENTO E INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1043,22 +1051,22 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>08/26</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Transporte de dos mil metros cúbicos (2.000 m³) de ripio arcilloso destinados al mantenimiento y mejoramiento de caminos de la jurisdicción comunal de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás documentación</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “NUEVA INSTALACION ELECTRICA, CUBIERTA DE TECHO Y REFACCION DE BAÑOS ESCUELA Nº 1 “JOSE MARIA TEXIER” -SAN SALVADOR-DEPARTAMENTO SAN SALVADOR.”</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>14 de septiembre de 2026 - Hora: 10:00</t>
+          <t>DE LAS OFERTAS: el día 15 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1066,7 +1074,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1084,7 +1096,7 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>id-85e6cfd11c8a8889</t>
+          <t>id-fb80c8ade7a8651d</t>
         </is>
       </c>
     </row>
@@ -1099,39 +1111,39 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LICITACIÓN PÚBLICA</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>76/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>ADQUICION DE CAMIONES COMPACTADORES DE CARGA TRASERA RSU</t>
+          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>14-09-2026 08:00</t>
+          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1152,12 +1164,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Municipalidad de Paraná</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>id-ccdfae2a7ede4696</t>
+          <t>id-952aef4c115d8f12</t>
         </is>
       </c>
     </row>
@@ -1172,14 +1184,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE HERRERA — DPTO. URUGUAY, ENTRE RIOS</t>
+          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1189,22 +1201,22 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>01-2026</t>
+          <t>27/2026</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de vehículo 0 km destinado al traslado de personas tipo van, con capacidad para 11 plazas (1 conductor + 10 pasajeros), motorización a nafta/diesel, según pliego de especificaciones técnicas</t>
+          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 15/09/2026, a las 11:00 hs. en el Edificio Municipal de Herrera, sito en Av. H. Bozzolo, Nº 165,</t>
+          <t>16 de septiembre de 2026 - Hora: 10:00</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1212,11 +1224,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1234,7 +1242,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>id-28313c7a9524d0ee</t>
+          <t>id-608017f47f903d65</t>
         </is>
       </c>
     </row>
@@ -1249,14 +1257,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARI</t>
+          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1266,22 +1274,22 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>014/2026</t>
+          <t>06/26</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la provisión de materiales – 500 (quinientos) m3 de Hormigón elaborado Tipo H30, Reglamento CIRSOC 201, para ser utilizados en la obra de construcción de pavimento en c alle Moreno entre Av. 1° de Mayo y Guarumba de nuestra ciudad</t>
+          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>15 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1291,7 +1299,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>$ 82.500,00. - (PESOS OCHENTA Y DOS MIL QUINIENTOS CON 00/100)</t>
+          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -1311,7 +1319,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>id-9e58cc9ec0b69356</t>
+          <t>id-9dbdaa6090d92bd4</t>
         </is>
       </c>
     </row>
@@ -1326,14 +1334,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO E INFRAESTRUCTURA</t>
+          <t>MUNICIPALIDAD DE SEGUÍ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1343,22 +1351,22 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>08/26</t>
+          <t>08-2026</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “NUEVA INSTALACION ELECTRICA, CUBIERTA DE TECHO Y REFACCION DE BAÑOS ESCUELA Nº 1 “JOSE MARIA TEXIER” -SAN SALVADOR-DEPARTAMENTO SAN SALVADOR.”</t>
+          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 15 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1368,7 +1376,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>$ 100 (Cien)</t>
+          <t>Gratuito</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -1388,7 +1396,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>id-fb80c8ade7a8651d</t>
+          <t>id-90c3d1f38f49418a</t>
         </is>
       </c>
     </row>
@@ -1403,14 +1411,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1420,22 +1428,22 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>015/2026</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Nueva instalación eléctrica, cubierta de techo y refacción de baños Escuela N° 1 "José María Texier", San Salvador</t>
+          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>martes, 15 de septiembre de 2026 - 10:00hs</t>
+          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1443,7 +1451,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
+        </is>
+      </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1456,12 +1468,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>id-952aef4c115d8f12</t>
+          <t>id-74dfdad7e5f9d048</t>
         </is>
       </c>
     </row>
@@ -1476,14 +1488,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>URUGUAY — MUNICIPALIDAD DE CONCEPCIÓN DEL URUGUAY</t>
+          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1493,22 +1505,22 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>27/2026</t>
+          <t>09/26</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>“Adquisición de seiscientas (600) Luminarias Leds para Alumbrado Público”, en un todo de acuerdo a los Pliegos de Bases, Condiciones Particulares y demás docum entación</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>16 de septiembre de 2026 - Hora: 10:00</t>
+          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1516,7 +1528,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1534,7 +1550,7 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>id-608017f47f903d65</t>
+          <t>id-6a4a84712fd41a03</t>
         </is>
       </c>
     </row>
@@ -1549,14 +1565,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>GOBIERNO DE ENTRE RÍOS — UNIDAD CENTRAL DE CONTRATACIONES</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1566,22 +1582,22 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>06/26</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Adquirir materiales de construcción (chapas, rollos de film de polietileno, tirantes, clavos y clavadoras)</t>
+          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Unidad Central de Contrataciones, el día 17/09/26 a las 09:00 horas</t>
+          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1589,11 +1605,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>PESOS CINCUENTA MIL ($ 50.000)</t>
-        </is>
-      </c>
+      <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1606,12 +1618,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>id-9dbdaa6090d92bd4</t>
+          <t>id-885d4847519dfd48</t>
         </is>
       </c>
     </row>
@@ -1626,14 +1638,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE SEGUÍ</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1643,22 +1655,22 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>08-2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de Materiales para la Obra Pública, según Planificación del “Proyecto: Vestuarios, Sanitarios y Salón de Us os Múltiples – Gimnasio Municipal”</t>
+          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026 a las 10:00 hs, en el Edificio Municipal</t>
+          <t>21/09/2026 HORA: 10:00 HS</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1668,7 +1680,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Gratuito</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -1688,7 +1700,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>id-90c3d1f38f49418a</t>
+          <t>id-6ddfa0f2f1aa296d</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1722,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FEDERACION — MUNICIPALIDAD DE CHAJARÍ</t>
+          <t>COLON — MUNICIPALIDAD DE COLON</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1718,24 +1730,20 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>015/2026</t>
-        </is>
-      </c>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Llamar a LICITACION PUBLICA tendiente a la Provisión de 400 (CUATROCIENTOS) Equipos de luminarias para iluminación pública con tecnología LED 150, para ser colocadas en distintos sectores, con el fin de mejorar el aspecto de nuestra ciudad</t>
+          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>18 DE SEPTIEMBRE DE 2026 - HORA: 10:00. (DIEZ)</t>
+          <t>24 de SEPTIEMBRE de 2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1745,7 +1753,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>$ 90.000,00. - (PESOS NOVENTA MIL CON 00/100)</t>
+          <t>Sin Cargo</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
@@ -1765,7 +1773,7 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>id-74dfdad7e5f9d048</t>
+          <t>id-bc610b64999d147d</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1795,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PARANA — MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1797,34 +1805,30 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>09/26</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “AMPLIACION - RECONSTRUCCION DE PISOS Y CONTRAPISOS -IMPERMEABILIZACION LOSAS- INSTALACION ELECTRICA-ESCUELA SECUNDARIA ADULTOS Nº 1 “DR. LUIS AGOTE” -NOGOYA-DEPARTAMENTO NOGOYA.”</t>
+          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 18 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr"/>
       <c r="L18" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -1842,7 +1846,7 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>id-6a4a84712fd41a03</t>
+          <t>id-d97b43a99f1e1824</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1868,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1879,22 +1883,22 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Ampliación - Reconstrucción de pisos y contrapisos - Impermeabilización losas - Instalación eléctrica - Escuela Secundaria Adultos N° 1 "Dr. Luis Agote", Nogoyá</t>
+          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>viernes, 18 de septiembre de 2026 - 10:00hs</t>
+          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr"/>
@@ -1910,19 +1914,19 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>id-885d4847519dfd48</t>
+          <t>id-f8fab7a7b3a06a2d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1930,49 +1934,49 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>“PROVISIÓN, TRASLADO, EXCAVACIÓN, PREPARACIÓN DEL TERRENO, INSTALACIÓN Y PUESTA EN FUNCIONAMIENTO DE UNA (1) PISCINA INFANTIL, CON EQUIPAMIENTO Y ACCESORIOS”</t>
+          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>21/09/2026 HORA: 10:00 HS</t>
+          <t>28/9/2026 – 10:00 horas</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>SIN COSTO</t>
+          <t>$25.000,00</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -1987,12 +1991,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Municipalidad de Crespo</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>id-6ddfa0f2f1aa296d</t>
+          <t>id-1609ce58e128c413</t>
         </is>
       </c>
     </row>
@@ -2007,14 +2011,14 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>COLON — MUNICIPALIDAD DE COLON</t>
+          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2022,20 +2026,24 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>08/2026</t>
+        </is>
+      </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE MATERIALES PARA OBRAS COMPLEMENTARIAS Al PLAN DE PAVIMENTACIÓN URBANA”</t>
+          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>24 de SEPTIEMBRE de 2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2045,7 +2053,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>Sin Cargo</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -2065,7 +2073,7 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>id-bc610b64999d147d</t>
+          <t>id-1590925c21c7e363</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2095,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>COLON — COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2097,30 +2105,34 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>REMODELACI ON Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE – DPTO. COLON – PROVINCIA DE ENTRE RIOS de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIU</t>
+          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr"/>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>$ 100 (Cien)</t>
+        </is>
+      </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2138,7 +2150,7 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>id-d97b43a99f1e1824</t>
+          <t>id-75a5c9dd5b4aa6f3</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2172,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>COMISIÓN ADMINISTRADORA PARA EL FONDO ESPECIAL DE SALTO GRANDE</t>
+          <t>Arquitectura y Construcciones (DGAyC)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2170,27 +2182,27 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>“REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS” de acuerdo a las condiciones que se detallan en los pliegos, aprobados por el Directorio de C.A.F.E.S.G</t>
+          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA C AFESG – CALLE SAN JUAN Nº 2097 – CI</t>
+          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr"/>
@@ -2206,69 +2218,65 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Min. Planeamiento (provincia)</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>id-f8fab7a7b3a06a2d</t>
+          <t>id-46c6d9f1f9210d1e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>5/2026</t>
+          <t>001-2026</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 145 metros lineales de módulo canal premoldeado.</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
+          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>28/9/2026 – 10:00 horas</t>
+          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>$25.000,00</t>
+          <t>SIN COSTO</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
@@ -2283,12 +2291,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Municipalidad de Crespo</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>id-1609ce58e128c413</t>
+          <t>id-b7b0120caf49d551</t>
         </is>
       </c>
     </row>
@@ -2298,19 +2306,19 @@
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LA PAZ — MUNICIPALIDAD DE SANTA ELENA</t>
+          <t>MUNICIPALIDAD DE URDINARRAIN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2320,22 +2328,18 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>“PROVISION DE “UN (1) CAMIÓN CON CAJA VOLCADORA 0 KM”. -PRESUPUESTO: ($ 129.000.000,00), PESOS CIENTO VEINTINUEVE MILLONES IVA INCL UIDO</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>29/09/2026</t>
-        </is>
-      </c>
+          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2343,11 +2347,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K25" s="4" t="inlineStr"/>
       <c r="L25" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>id-1590925c21c7e363</t>
+          <t>id-7a200161bcc9b02b</t>
         </is>
       </c>
     </row>
@@ -2375,19 +2375,19 @@
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MINISTERIO DE PLANEAMIENTO EE INFRAESTRUCTURA</t>
+          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2397,22 +2397,18 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Provisión de Materiales y Mano de Obra según Pliego para la Obra: “ IMPERMEABILIZACION CUBIERTA DE TECHOS, REPARACION DE MAMPOSTERIAS Y PINTURA ESCUELA Nº 2 “ALVAREZ CONDARCO”-CHAJARI-DEPARTAME NTO FEDERACION.”</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>DE LAS OFERTAS: el día 30 de Septiembre de 2026 a las 10:00 hs</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2420,11 +2416,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>$ 100 (Cien)</t>
-        </is>
-      </c>
+      <c r="K26" s="4" t="inlineStr"/>
       <c r="L26" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2442,7 +2434,7 @@
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>id-75a5c9dd5b4aa6f3</t>
+          <t>id-511256e6329e386a</t>
         </is>
       </c>
     </row>
@@ -2452,44 +2444,40 @@
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Arquitectura y Construcciones (DGAyC)</t>
+          <t>Boletín Oficial</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>10/2026</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Impermeabilización cubierta de techos, reparación de mamposterías y pintura Escuela N° 2 "Alvarez Condarco", Chajarí</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>ENERSA convoca a la Licitación Nº 2026- 1227 con el objeto de la provi sión de postes de hormigón para líneas</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>miércoles, 30 de septiembre de 2026 - 10:00hs</t>
+          <t>Ver boletín</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2510,19 +2498,19 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Min. Planeamiento (provincia)</t>
+          <t>Boletín Oficial de Entre Ríos</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>id-46c6d9f1f9210d1e</t>
+          <t>id-e90021854bcee649</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2530,14 +2518,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GUALEGUAYCHU — MUNICIPIO DE GILBERT</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2547,18 +2535,18 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>001-2026</t>
+          <t>03/26</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>LLAMADO A LICITACIÓN PÚBLICA Nº 001 -2026 – DECRETO N° 134/2026 DEPARTAMENTO EJECUTIVO. “CONTRATACION DE MANO DE OBRA PARA LA CONSTRUCCION DE UNA PILETA SEMI - OLIMPICA Y OBRAS COMPLEMENTARIAS EN EL MARCO DEL PLIEGO DE BASES Y CONDICIONES GENERALES Y PLIEGO DE CONDICIONES PARTICULARES Y ESPECIFICACIONES TECNICAS”</t>
+          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Miércoles Treinta (30) de septiembre de 2026 a las 09:30 horas, en el Honorable Concejo Deliberante del M</t>
+          <t>Publicada 21/08/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2566,11 +2554,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>SIN COSTO</t>
-        </is>
-      </c>
+      <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2583,19 +2567,19 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-b7b0120caf49d551</t>
+          <t>id-2b877612500f72b1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2603,14 +2587,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE URDINARRAIN</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2620,18 +2604,18 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Adquisición de 300 M³ de hormigón elaborado H -21 (puesto en obra)</t>
+          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Publicada 09/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2652,19 +2636,19 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-7a200161bcc9b02b</t>
+          <t>id-b8ac4ddaa39b00be</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2672,14 +2656,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Vehículos</t>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GUALEGUAY — COMUNA DE SEXTO DISTRITO</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2694,13 +2678,13 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN MAQUINARIA VIAL PARA COMUNA SEXTO DISTRITO – MOTONIVELADORA ARTICULADA”</t>
+          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Publicada 05/06/2026 — ver pliego</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2721,19 +2705,19 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-511256e6329e386a</t>
+          <t>id-d0b9714db86e5226</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2741,35 +2725,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Boletín Oficial</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>05/2025</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>ENERSA convoca a la Licitación Nº 2026- 1227 con el objeto de la provi sión de postes de hormigón para líneas</t>
+          <t>NOGOYA 19 VIVIENDAS</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Ver boletín</t>
+          <t>Publicada 11/12/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2790,19 +2774,19 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-e90021854bcee649</t>
+          <t>id-22811eab8859abaf</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2827,18 +2811,18 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>06/2025</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
+          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
+          <t>Publicada 18/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2846,11 +2830,7 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>$ 120.976,01</t>
-        </is>
-      </c>
+      <c r="K32" s="4" t="inlineStr"/>
       <c r="L32" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2868,14 +2848,14 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-07ddb93a12c5a870</t>
+          <t>id-c019bf4a08989c09</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2898,20 +2878,16 @@
           <t>Licitación Pública</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Concurso de Precio N° 02/2025</t>
+          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
+          <t>Publicada 11/11/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2937,14 +2913,14 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-7c1bf02160a66f67</t>
+          <t>id-ebeeb6a87e688d85</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2959,28 +2935,28 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Concurso</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>01/26</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
+          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 23/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -3001,19 +2977,19 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>id-9a16884dd5a64a49</t>
+          <t>id-34c85bcdb9b1123f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3021,35 +2997,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Licitación</t>
+          <t>Licitación Pública</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>2026-1227</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego</t>
+          <t>Publicada 08/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3070,12 +3046,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>ENERSA</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>id-0691eb485d7548eb</t>
+          <t>id-75bfffae63b7eedc</t>
         </is>
       </c>
     </row>
@@ -3090,14 +3066,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3107,18 +3083,18 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>10-2026</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -3139,12 +3115,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>id-bdd0abb0374c3f42</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
@@ -3159,14 +3135,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>IAPV (Vivienda)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3176,18 +3152,18 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>09-2026</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3208,12 +3184,12 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>IAPV — Viviendas</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>id-42c411be9946d956</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
@@ -3228,35 +3204,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CAFESG (Salto Grande)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>04-2026</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Ver pliego — figura como Pendiente</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -3277,17 +3253,293 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
+          <t>Vialidad Entre Ríos (DPV)</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>id-9a16884dd5a64a49</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ENERSA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Licitación</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>2026-1227</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr"/>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>ENERSA</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>id-0691eb485d7548eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
-      <c r="O38" s="4" t="inlineStr">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>10-2026</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego — figura como Pendiente</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr"/>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>id-bdd0abb0374c3f42</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>09-2026</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego — figura como Pendiente</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>id-42c411be9946d956</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Revisar fecha</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Licitación Privada</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>04-2026</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego — figura como Pendiente</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>Ver pliego</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>ver licitación</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>CAFESG (Salto Grande)</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
         <is>
           <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O38"/>
+  <autoFilter ref="A1:O42"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3363,6 +3615,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Licitaciones-Entre-Rios.xlsx
+++ b/Licitaciones-Entre-Rios.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Licitaciones'!$A$1:$O$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -572,7 +572,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -726,7 +726,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE HERRERA — DPTO. URUGUAY, ENTRE RIOS</t>
+          <t>MUNICIPALIDAD DE HERRERA — DPTO. URUGUAY, ENTRE RÍOS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -949,7 +949,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1480,7 +1480,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1715,9 +1715,9 @@
           <t>Vigente</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1780,7 +1780,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1853,7 +1853,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Boletín Oficial de Entre Ríos</t>
+          <t>Boletín Oficial de Entre Ríos + CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2303,7 +2303,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2372,7 +2372,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2441,7 +2441,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2535,18 +2535,18 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>03/26</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>TERMINACIÓN VILLA PARANECITO 50 VIVIENDAS - DEPARTAMENTO ISLAS DEL IBICUY</t>
+          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Publicada 21/08/2026 — ver pliego</t>
+          <t>Publicada 06/10/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2554,7 +2554,11 @@
           <t>Ver pliego</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>$ 120.976,01</t>
+        </is>
+      </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
           <t>ver licitación</t>
@@ -2572,14 +2576,14 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>id-2b877612500f72b1</t>
+          <t>id-07ddb93a12c5a870</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2604,18 +2608,18 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>HERRERA 18 VIVIENDAS - DEPARTAMENTO URUGUAY</t>
+          <t>Concurso de Precio N° 02/2025</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Publicada 09/06/2026 — ver pliego</t>
+          <t>Publicada 19/06/2025 — ver pliego</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2641,14 +2645,14 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>id-b8ac4ddaa39b00be</t>
+          <t>id-7c1bf02160a66f67</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2663,28 +2667,28 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Concurso</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>01/26</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>LARROQUE 18 VIVIENDAS - DEPARTAMENTO GUALEGUAYCHU</t>
+          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Publicada 05/06/2026 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2705,19 +2709,19 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>Vialidad Entre Ríos (DPV)</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>id-d0b9714db86e5226</t>
+          <t>id-9a16884dd5a64a49</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2725,35 +2729,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Materiales</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>Licitación</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>05/2025</t>
+          <t>2026-1227</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>NOGOYA 19 VIVIENDAS</t>
+          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/12/2025 — ver pliego</t>
+          <t>Ver pliego</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2774,19 +2778,19 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>ENERSA</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>id-22811eab8859abaf</t>
+          <t>id-0691eb485d7548eb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2794,14 +2798,14 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2811,18 +2815,18 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>06/2025</t>
+          <t>10-2026</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>SAN JAIME DE LA FRONTERA 15 VIVIENDAS</t>
+          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Publicada 18/11/2025 — ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2843,19 +2847,19 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>id-c019bf4a08989c09</t>
+          <t>id-bdd0abb0374c3f42</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2863,31 +2867,35 @@
           <t>Revisar fecha</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>IAPV (Vivienda)</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr"/>
+          <t>Licitación Privada</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>04-2026</t>
+        </is>
+      </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>PARANÁ 2 VIVIENDAS - PROTOTIPO DUPLEX 2 DORMITORIOS</t>
+          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Publicada 11/11/2025 — ver pliego</t>
+          <t>Ver pliego — figura como Pendiente</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2908,638 +2916,17 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>IAPV — Viviendas</t>
+          <t>CAFESG (Salto Grande)</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>id-ebeeb6a87e688d85</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>IAPV (Vivienda)</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>04/2025</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>CHAJARI 10 VIVIENDAS - MAIPER (P</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr"/>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 23/10/2025 — ver pliego</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr"/>
-      <c r="L34" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M34" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>IAPV — Viviendas</t>
-        </is>
-      </c>
-      <c r="O34" s="4" t="inlineStr">
-        <is>
-          <t>id-34c85bcdb9b1123f</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>IAPV (Vivienda)</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>03/2025</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>TERMINACIÓN PARANÁ 30 VIVIENDAS - VICOER</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr"/>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 08/10/2025 — ver pliego</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr"/>
-      <c r="L35" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M35" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>IAPV — Viviendas</t>
-        </is>
-      </c>
-      <c r="O35" s="4" t="inlineStr">
-        <is>
-          <t>id-75bfffae63b7eedc</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>IAPV (Vivienda)</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>CONCORDIA 18 VIVIENDAS EN DUPLEX</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr"/>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 06/10/2025 — ver pliego</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr"/>
-      <c r="L36" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M36" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>IAPV — Viviendas</t>
-        </is>
-      </c>
-      <c r="O36" s="4" t="inlineStr">
-        <is>
-          <t>id-07ddb93a12c5a870</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>IAPV (Vivienda)</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>02/2025</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>Concurso de Precio N° 02/2025</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr"/>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>Publicada 19/06/2025 — ver pliego</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr"/>
-      <c r="L37" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M37" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>IAPV — Viviendas</t>
-        </is>
-      </c>
-      <c r="O37" s="4" t="inlineStr">
-        <is>
-          <t>id-7c1bf02160a66f67</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Concurso</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>01/26</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>PROYECTO EJECUTIVO DE LA OBRA: RUTA PROVINCIAL A08 – TRAMO: R.N. Nº12 – VILLA PARANACITO – CONSTRUCCIÓN DE CALZADA, RECONSTRUCCIÓN DE LA CALZADA EXISTENTE, VERIFICACIÓN, REPARACIÓN Y DISEÑO DE OBRAS DE ARTE -DEPARTAMENTO: ISLAS DEL IBICUY – PROVINCIA: ENTRE RÍOS – LONGITUD APROXIMADA DEL TRAMO: 20,685 km.- CONSULTA DE PLIEGOS: www.dpver.gov.ar – […]</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr"/>
-      <c r="L38" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M38" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Vialidad Entre Ríos (DPV)</t>
-        </is>
-      </c>
-      <c r="O38" s="4" t="inlineStr">
-        <is>
-          <t>id-9a16884dd5a64a49</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>Materiales</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>ENERSA</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Licitación</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>2026-1227</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>Adquisición Postes de hormigón para líneas aéreas de energía eléctrica</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr"/>
-      <c r="L39" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M39" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>ENERSA</t>
-        </is>
-      </c>
-      <c r="O39" s="4" t="inlineStr">
-        <is>
-          <t>id-0691eb485d7548eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>10-2026</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>REMODELACION Y TERMINACION ESCUELA Nº 54 “CARLOS SOURIGUES” - BARRIO PERUCHO VERNA – SAN JOSE– DPTO. COLON – PROVINCIA DE ENTRE RIOS- Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 12:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego — figura como Pendiente</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr"/>
-      <c r="L40" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M40" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="O40" s="4" t="inlineStr">
-        <is>
-          <t>id-bdd0abb0374c3f42</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>09-2026</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>REFACCION, RESTAURACION Y PUESTA EN VALOR – ESCUELA N° 15 NORMAL “DOMINGO FAUSTINO SARMIENTO” – CIUDAD DE CONCORDIA – DEPARTAMENTO CONCORDIA – PROVINCIA DE ENTRE RIOS Apertura: Jueves 24 DE SEPTIEMBRE DEL AÑO 2026.- Hora: 10:00 Lugar: OFICINAS CENTRALES DE LA CAFESG – CALLE SAN JUAN Nº 2097 – CIUDAD DE CONCORDIA – ENTRE RIOS.-</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego — figura como Pendiente</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr"/>
-      <c r="L41" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M41" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="O41" s="4" t="inlineStr">
-        <is>
-          <t>id-42c411be9946d956</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Revisar fecha</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Licitación Privada</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>04-2026</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>REFACCION Y AMPLIACION ESCUELA Nº 56 “HIPOLITO YRIGOYEN“– CIUDAD DE COLON - DEPARTAMENTO COLON - PROVINCIA DE ENTRE RÍOS Apertura: La apertura de las propuestas se realizará el día Viernes 11 de Septiembre de 2026 a las 10:00 horas, en las Oficinas de C.A.F.E.S.G. de la Ciudad de Concordia, sitas en Calle San Juan Nº 2097.</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego — figura como Pendiente</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>Ver pliego</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="6" t="inlineStr">
-        <is>
-          <t>ver licitación</t>
-        </is>
-      </c>
-      <c r="M42" s="6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>CAFESG (Salto Grande)</t>
-        </is>
-      </c>
-      <c r="O42" s="4" t="inlineStr">
-        <is>
           <t>id-023b6b75e7014a9c</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O42"/>
+  <autoFilter ref="A1:O33"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -3605,24 +2992,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
